--- a/data/informes/cuadro_10_4.xlsx
+++ b/data/informes/cuadro_10_4.xlsx
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>30277190.37</v>
+        <v>35043831.29</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.198176</v>
+        <v>0.229375</v>
       </c>
     </row>
     <row r="5">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>29720669.84</v>
+        <v>34477521.72</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.981619</v>
+        <v>0.98384</v>
       </c>
       <c r="E5" s="9" t="n"/>
     </row>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>9944312.57</v>
+        <v>11723255.2</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.328442</v>
+        <v>0.334531</v>
       </c>
       <c r="E6" s="9" t="n"/>
     </row>
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>8429199.68</v>
+        <v>9809245.060000001</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.278401</v>
+        <v>0.279914</v>
       </c>
       <c r="E7" s="9" t="n"/>
     </row>
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>5837841.14</v>
+        <v>6758092.8</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.192813</v>
+        <v>0.192847</v>
       </c>
       <c r="E8" s="9" t="n"/>
     </row>
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>5488736.75</v>
+        <v>6166348.96</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.181283</v>
+        <v>0.175961</v>
       </c>
       <c r="E9" s="9" t="n"/>
     </row>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>550758.65</v>
+        <v>560547.6899999999</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.018191</v>
+        <v>0.015996</v>
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>550758.65</v>
+        <v>560547.6899999999</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.018191</v>
+        <v>0.015996</v>
       </c>
       <c r="E12" s="9" t="n"/>
     </row>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>37666567.75</v>
+        <v>33138329.57</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.246542</v>
+        <v>0.216903</v>
       </c>
     </row>
     <row r="14">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>36782889.99</v>
+        <v>32254651.81</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.9765389999999999</v>
+        <v>0.9733339999999999</v>
       </c>
       <c r="E14" s="9" t="n"/>
     </row>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>480030.8</v>
+        <v>417203.58</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.012744</v>
+        <v>0.01259</v>
       </c>
       <c r="E15" s="9" t="n"/>
     </row>
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>476077.97</v>
+        <v>405761.08</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.012639</v>
+        <v>0.012244</v>
       </c>
       <c r="E16" s="9" t="n"/>
     </row>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1005503.65</v>
+        <v>804964.64</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.026695</v>
+        <v>0.024291</v>
       </c>
       <c r="E17" s="9" t="n"/>
     </row>
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>207134.15</v>
+        <v>181469.16</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.005499</v>
+        <v>0.005476</v>
       </c>
       <c r="E18" s="9" t="n"/>
     </row>
@@ -811,7 +811,7 @@
         <v>69722.34</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.001851</v>
+        <v>0.002104</v>
       </c>
       <c r="E19" s="9" t="n"/>
     </row>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>48976.71</v>
+        <v>34036.76</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.0013</v>
+        <v>0.001027</v>
       </c>
       <c r="E20" s="9" t="n"/>
     </row>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>199158.61</v>
+        <v>138363.23</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.005286999999999999</v>
+        <v>0.004175</v>
       </c>
       <c r="E21" s="9" t="n"/>
     </row>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>337362.34</v>
+        <v>325770.13</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.008957</v>
+        <v>0.009830999999999999</v>
       </c>
       <c r="E22" s="9" t="n"/>
     </row>
@@ -884,10 +884,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>97844.02</v>
+        <v>70286.75</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.002598</v>
+        <v>0.002121</v>
       </c>
       <c r="E23" s="9" t="n"/>
     </row>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>1252056.22</v>
+        <v>1039308.13</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.033241</v>
+        <v>0.031363</v>
       </c>
       <c r="E24" s="9" t="n"/>
     </row>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>4703451.86</v>
+        <v>4661913.68</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.124871</v>
+        <v>0.14068</v>
       </c>
       <c r="E25" s="9" t="n"/>
     </row>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>3354963.31</v>
+        <v>3110514.18</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.08907</v>
+        <v>0.093865</v>
       </c>
       <c r="E26" s="9" t="n"/>
     </row>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>1670145.45</v>
+        <v>1663212.47</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.04434</v>
+        <v>0.05019</v>
       </c>
       <c r="E27" s="9" t="n"/>
     </row>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>1765583.31</v>
+        <v>1698668.23</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.046874</v>
+        <v>0.05126</v>
       </c>
       <c r="E28" s="9" t="n"/>
     </row>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>157466.56</v>
+        <v>122497.25</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.004181000000000001</v>
+        <v>0.003697</v>
       </c>
       <c r="E29" s="9" t="n"/>
     </row>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>136740.07</v>
+        <v>135705.36</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.00363</v>
+        <v>0.004095</v>
       </c>
       <c r="E30" s="9" t="n"/>
     </row>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>20820672.62</v>
+        <v>17375254.84</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.552763</v>
+        <v>0.5243249999999999</v>
       </c>
       <c r="E31" s="9" t="n"/>
     </row>
@@ -1096,7 +1096,7 @@
         <v>744905.22</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.019776</v>
+        <v>0.022479</v>
       </c>
       <c r="E34" s="9" t="n"/>
     </row>
@@ -1115,7 +1115,7 @@
         <v>138772.53</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.003684</v>
+        <v>0.004188</v>
       </c>
       <c r="E35" s="9" t="n"/>
     </row>
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>25865937.42</v>
+        <v>25376638.53</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.169303</v>
+        <v>0.1661</v>
       </c>
     </row>
     <row r="37">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>20721410.16</v>
+        <v>20940280.35</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.8011079999999999</v>
+        <v>0.825179</v>
       </c>
       <c r="E37" s="9" t="n"/>
     </row>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>501138.14</v>
+        <v>514564.36</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.019374</v>
+        <v>0.020277</v>
       </c>
       <c r="E38" s="9" t="n"/>
     </row>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>1703303.2</v>
+        <v>1710285.04</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.06585099999999999</v>
+        <v>0.067396</v>
       </c>
       <c r="E39" s="9" t="n"/>
     </row>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>546375.33</v>
+        <v>561361.01</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.021123</v>
+        <v>0.022121</v>
       </c>
       <c r="E40" s="9" t="n"/>
     </row>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>188463.54</v>
+        <v>196964.18</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.007286</v>
+        <v>0.007762</v>
       </c>
       <c r="E41" s="9" t="n"/>
     </row>
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>413903.03</v>
+        <v>431095.58</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.016002</v>
+        <v>0.016988</v>
       </c>
       <c r="E42" s="9" t="n"/>
     </row>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>732564.24</v>
+        <v>758128.24</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.028322</v>
+        <v>0.029875</v>
       </c>
       <c r="E43" s="9" t="n"/>
     </row>
@@ -1288,7 +1288,7 @@
         <v>543557.21</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.021014</v>
+        <v>0.02142</v>
       </c>
       <c r="E44" s="9" t="n"/>
     </row>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>315484.39</v>
+        <v>333619.42</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.012197</v>
+        <v>0.013147</v>
       </c>
       <c r="E45" s="9" t="n"/>
     </row>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>341314.62</v>
+        <v>327822.12</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.013196</v>
+        <v>0.012918</v>
       </c>
       <c r="E46" s="9" t="n"/>
     </row>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>166957.41</v>
+        <v>171152.2</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.006455</v>
+        <v>0.006744</v>
       </c>
       <c r="E47" s="9" t="n"/>
     </row>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>371104.24</v>
+        <v>367394.48</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.014347</v>
+        <v>0.014478</v>
       </c>
       <c r="E48" s="9" t="n"/>
     </row>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>844583.67</v>
+        <v>850744.66</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.032652</v>
+        <v>0.033525</v>
       </c>
       <c r="E49" s="9" t="n"/>
     </row>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>510883.48</v>
+        <v>516192.08</v>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.019751</v>
+        <v>0.020341</v>
       </c>
       <c r="E50" s="9" t="n"/>
     </row>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>1690474.65</v>
+        <v>1779349.1</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.065355</v>
+        <v>0.070118</v>
       </c>
       <c r="E51" s="9" t="n"/>
     </row>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>1920152.78</v>
+        <v>1928564.95</v>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.074235</v>
+        <v>0.075998</v>
       </c>
       <c r="E52" s="9" t="n"/>
     </row>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>566999.26</v>
+        <v>593160.45</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.021921</v>
+        <v>0.023374</v>
       </c>
       <c r="E53" s="9" t="n"/>
     </row>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>1543195.52</v>
+        <v>1543195.51</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.059661</v>
+        <v>0.060812</v>
       </c>
       <c r="E54" s="9" t="n"/>
     </row>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>765130.98</v>
+        <v>737439.21</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.029581</v>
+        <v>0.02906</v>
       </c>
       <c r="E55" s="9" t="n"/>
     </row>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>597157.73</v>
+        <v>578464.98</v>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.023087</v>
+        <v>0.022795</v>
       </c>
       <c r="E56" s="9" t="n"/>
     </row>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>324607.97</v>
+        <v>360358.1</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.01255</v>
+        <v>0.0142</v>
       </c>
       <c r="E57" s="9" t="n"/>
     </row>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>1826432.5</v>
+        <v>1848553.75</v>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.07061099999999999</v>
+        <v>0.07284500000000001</v>
       </c>
       <c r="E58" s="9" t="n"/>
     </row>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>609305.75</v>
+        <v>607723.89</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.023556</v>
+        <v>0.023948</v>
       </c>
       <c r="E59" s="9" t="n"/>
     </row>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="C60" s="8" t="n">
-        <v>597985.15</v>
+        <v>599582.1</v>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.023119</v>
+        <v>0.023627</v>
       </c>
       <c r="E60" s="9" t="n"/>
     </row>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>1535166.72</v>
+        <v>1492656.49</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.059351</v>
+        <v>0.05882</v>
       </c>
       <c r="E61" s="9" t="n"/>
     </row>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>335470.95</v>
+        <v>331900.3</v>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.01297</v>
+        <v>0.013079</v>
       </c>
       <c r="E62" s="9" t="n"/>
     </row>
@@ -1649,7 +1649,7 @@
         <v>151437.83</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.005855</v>
+        <v>0.005968</v>
       </c>
       <c r="E63" s="9" t="n"/>
     </row>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="C64" s="8" t="n">
-        <v>181404.3</v>
+        <v>199035.85</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.007013</v>
+        <v>0.007842999999999999</v>
       </c>
       <c r="E64" s="9" t="n"/>
     </row>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>896855.59</v>
+        <v>905977.28</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.034673</v>
+        <v>0.035701</v>
       </c>
       <c r="E65" s="9" t="n"/>
     </row>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="C66" s="8" t="n">
-        <v>5144527.26</v>
+        <v>4436358.18</v>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.198892</v>
+        <v>0.174821</v>
       </c>
       <c r="E66" s="9" t="n"/>
     </row>
@@ -1760,13 +1760,13 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>10969670.68</v>
+        <v>10896354.82</v>
       </c>
       <c r="D69" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>0.071801</v>
+        <v>0.07132100000000001</v>
       </c>
     </row>
     <row r="70">
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="C70" s="8" t="n">
-        <v>2584807.39</v>
+        <v>2524954.68</v>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.235632</v>
+        <v>0.231725</v>
       </c>
       <c r="E70" s="9" t="n"/>
     </row>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>4025610.16</v>
+        <v>4009694.33</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.366976</v>
+        <v>0.367985</v>
       </c>
       <c r="E71" s="9" t="n"/>
     </row>
@@ -1822,7 +1822,7 @@
         <v>410808.75</v>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.03745</v>
+        <v>0.037701</v>
       </c>
       <c r="E72" s="9" t="n"/>
     </row>
@@ -1841,7 +1841,7 @@
         <v>290168.86</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.026452</v>
+        <v>0.02663</v>
       </c>
       <c r="E73" s="9" t="n"/>
     </row>
@@ -1860,7 +1860,7 @@
         <v>1137344.84</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.103681</v>
+        <v>0.104378</v>
       </c>
       <c r="E74" s="9" t="n"/>
     </row>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>806019.0600000001</v>
+        <v>806019.05</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.073477</v>
+        <v>0.073971</v>
       </c>
       <c r="E75" s="9" t="n"/>
     </row>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="C76" s="8" t="n">
-        <v>792863.59</v>
+        <v>776947.77</v>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.07227800000000001</v>
+        <v>0.07130300000000001</v>
       </c>
       <c r="E76" s="9" t="n"/>
     </row>
@@ -1917,7 +1917,7 @@
         <v>345873.09</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.03153</v>
+        <v>0.031742</v>
       </c>
       <c r="E77" s="9" t="n"/>
     </row>
@@ -1936,7 +1936,7 @@
         <v>242531.97</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.022109</v>
+        <v>0.022258</v>
       </c>
       <c r="E78" s="9" t="n"/>
     </row>
@@ -1955,7 +1955,7 @@
         <v>3855737.54</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.351491</v>
+        <v>0.3538559999999999</v>
       </c>
       <c r="E79" s="9" t="n"/>
     </row>
@@ -1974,7 +1974,7 @@
         <v>1927287.27</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.175692</v>
+        <v>0.176874</v>
       </c>
       <c r="E80" s="9" t="n"/>
     </row>
@@ -1993,7 +1993,7 @@
         <v>1488552.09</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.135697</v>
+        <v>0.13661</v>
       </c>
       <c r="E81" s="9" t="n"/>
     </row>
@@ -2012,7 +2012,7 @@
         <v>439898.18</v>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.040101</v>
+        <v>0.040371</v>
       </c>
       <c r="E82" s="9" t="n"/>
     </row>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>503515.59</v>
+        <v>505968.27</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.045901</v>
+        <v>0.046435</v>
       </c>
       <c r="E83" s="9" t="n"/>
     </row>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="C86" s="8" t="n">
-        <v>406420.75</v>
+        <v>408873.43</v>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.037049</v>
+        <v>0.037524</v>
       </c>
       <c r="E86" s="9" t="n"/>
     </row>
@@ -2107,7 +2107,7 @@
         <v>51418.56</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.004687</v>
+        <v>0.004719</v>
       </c>
       <c r="E87" s="9" t="n"/>
     </row>
@@ -2126,7 +2126,7 @@
         <v>45676.28</v>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.004164</v>
+        <v>0.004192</v>
       </c>
       <c r="E88" s="9" t="n"/>
     </row>
@@ -2142,13 +2142,13 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>5155076.14</v>
+        <v>5150926.76</v>
       </c>
       <c r="D89" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>0.033742</v>
+        <v>0.033715</v>
       </c>
     </row>
     <row r="90">
@@ -2166,7 +2166,7 @@
         <v>1501527.08</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.291272</v>
+        <v>0.291506</v>
       </c>
       <c r="E90" s="9" t="n"/>
     </row>
@@ -2185,7 +2185,7 @@
         <v>3061799.43</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.593939</v>
+        <v>0.594417</v>
       </c>
       <c r="E91" s="9" t="n"/>
     </row>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>463439.2</v>
+        <v>459289.82</v>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.08990000000000001</v>
+        <v>0.08916600000000001</v>
       </c>
       <c r="E92" s="9" t="n"/>
     </row>
@@ -2242,7 +2242,7 @@
         <v>45523.13</v>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.008831</v>
+        <v>0.008838</v>
       </c>
       <c r="E94" s="9" t="n"/>
     </row>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>33138529.15</v>
+        <v>33056139.51</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>0.216904</v>
+        <v>0.216365</v>
       </c>
     </row>
     <row r="96">
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>1016723.03</v>
+        <v>1058971.57</v>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.030681</v>
+        <v>0.032036</v>
       </c>
       <c r="E96" s="9" t="n"/>
     </row>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>752535.42</v>
+        <v>763077.3100000001</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.022709</v>
+        <v>0.023084</v>
       </c>
       <c r="E97" s="9" t="n"/>
     </row>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="C98" s="8" t="n">
-        <v>157645.65</v>
+        <v>157645.66</v>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.004757</v>
+        <v>0.004769</v>
       </c>
       <c r="E98" s="9" t="n"/>
     </row>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>80467.31</v>
+        <v>101726.29</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.002428</v>
+        <v>0.003077</v>
       </c>
       <c r="E99" s="9" t="n"/>
     </row>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="C100" s="8" t="n">
-        <v>26074.65</v>
+        <v>36522.31</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.000787</v>
+        <v>0.001105</v>
       </c>
       <c r="E100" s="9" t="n"/>
     </row>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>8595315.34</v>
+        <v>8646870.59</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.259375</v>
+        <v>0.261581</v>
       </c>
       <c r="E101" s="9" t="n"/>
     </row>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="C102" s="8" t="n">
-        <v>713180.03</v>
+        <v>688643.96</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.021521</v>
+        <v>0.020833</v>
       </c>
       <c r="E102" s="9" t="n"/>
     </row>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>358450.85</v>
+        <v>374923.69</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.010817</v>
+        <v>0.011342</v>
       </c>
       <c r="E103" s="9" t="n"/>
     </row>
@@ -2434,7 +2434,7 @@
         <v>295706.8</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.008923</v>
+        <v>0.008945999999999999</v>
       </c>
       <c r="E104" s="9" t="n"/>
     </row>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>59022.38</v>
+        <v>18013.47</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.001781</v>
+        <v>0.000545</v>
       </c>
       <c r="E105" s="9" t="n"/>
     </row>
@@ -2472,7 +2472,7 @@
         <v>2111306.74</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.063712</v>
+        <v>0.06387</v>
       </c>
       <c r="E106" s="9" t="n"/>
     </row>
@@ -2491,7 +2491,7 @@
         <v>398388.1</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.012022</v>
+        <v>0.012052</v>
       </c>
       <c r="E107" s="9" t="n"/>
     </row>
@@ -2510,7 +2510,7 @@
         <v>293362.97</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.008853</v>
+        <v>0.008874999999999999</v>
       </c>
       <c r="E108" s="9" t="n"/>
     </row>
@@ -2529,7 +2529,7 @@
         <v>105025.14</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.003169</v>
+        <v>0.003177</v>
       </c>
       <c r="E109" s="9" t="n"/>
     </row>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="C110" s="8" t="n">
-        <v>6120808.4</v>
+        <v>6042348.45</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.184704</v>
+        <v>0.182791</v>
       </c>
       <c r="E110" s="9" t="n"/>
     </row>
@@ -2567,7 +2567,7 @@
         <v>680326.6899999999</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.02053</v>
+        <v>0.020581</v>
       </c>
       <c r="E111" s="9" t="n"/>
     </row>
@@ -2586,7 +2586,7 @@
         <v>288005.19</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.008690999999999999</v>
+        <v>0.008713</v>
       </c>
       <c r="E112" s="9" t="n"/>
     </row>
@@ -2605,7 +2605,7 @@
         <v>1113639.21</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.033606</v>
+        <v>0.033689</v>
       </c>
       <c r="E113" s="9" t="n"/>
     </row>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="C114" s="8" t="n">
-        <v>274959.59</v>
+        <v>274474.32</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.008297000000000001</v>
+        <v>0.008303</v>
       </c>
       <c r="E114" s="9" t="n"/>
     </row>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>1085614.77</v>
+        <v>1076083.54</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.03276</v>
+        <v>0.032553</v>
       </c>
       <c r="E115" s="9" t="n"/>
     </row>
@@ -2662,7 +2662,7 @@
         <v>1127119.4</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.034012</v>
+        <v>0.034097</v>
       </c>
       <c r="E116" s="9" t="n"/>
     </row>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>153268.64</v>
+        <v>138377.6</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.004625000000000001</v>
+        <v>0.004186</v>
       </c>
       <c r="E117" s="9" t="n"/>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="C118" s="8" t="n">
-        <v>1397874.91</v>
+        <v>1344322.5</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.042183</v>
+        <v>0.040668</v>
       </c>
       <c r="E118" s="9" t="n"/>
     </row>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>14182807.5</v>
+        <v>14109610.09</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.4279849999999999</v>
+        <v>0.426838</v>
       </c>
       <c r="E119" s="9" t="n"/>
     </row>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="C120" s="8" t="n">
-        <v>2180792.7</v>
+        <v>2131582.51</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.06580800000000001</v>
+        <v>0.064484</v>
       </c>
       <c r="E120" s="9" t="n"/>
     </row>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>1071901.91</v>
+        <v>1054468.78</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.032346</v>
+        <v>0.031899</v>
       </c>
       <c r="E121" s="9" t="n"/>
     </row>
@@ -2776,7 +2776,7 @@
         <v>89213.45</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.002692</v>
+        <v>0.002699</v>
       </c>
       <c r="E122" s="9" t="n"/>
     </row>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>704192.0600000001</v>
+        <v>697637.97</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.02125</v>
+        <v>0.021105</v>
       </c>
       <c r="E123" s="9" t="n"/>
     </row>
@@ -2833,7 +2833,7 @@
         <v>2564834.08</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.07739699999999999</v>
+        <v>0.07759000000000001</v>
       </c>
       <c r="E125" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         <v>2374472.67</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.07165300000000001</v>
+        <v>0.07183200000000001</v>
       </c>
       <c r="E126" s="9" t="n"/>
     </row>
@@ -2871,7 +2871,7 @@
         <v>1485694.33</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.044833</v>
+        <v>0.04494500000000001</v>
       </c>
       <c r="E127" s="9" t="n"/>
     </row>
@@ -2890,7 +2890,7 @@
         <v>626217.8</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.018897</v>
+        <v>0.018944</v>
       </c>
       <c r="E128" s="9" t="n"/>
     </row>
@@ -2909,7 +2909,7 @@
         <v>469180.61</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.014158</v>
+        <v>0.014193</v>
       </c>
       <c r="E129" s="9" t="n"/>
     </row>
@@ -2928,7 +2928,7 @@
         <v>2005483.64</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.060518</v>
+        <v>0.060669</v>
       </c>
       <c r="E130" s="9" t="n"/>
     </row>
@@ -2947,7 +2947,7 @@
         <v>315644.06</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.009525</v>
+        <v>0.009549</v>
       </c>
       <c r="E131" s="9" t="n"/>
     </row>
@@ -2966,7 +2966,7 @@
         <v>218921.74</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.006606</v>
+        <v>0.006623</v>
       </c>
       <c r="E132" s="9" t="n"/>
     </row>
@@ -2985,7 +2985,7 @@
         <v>76258.46000000001</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.002301</v>
+        <v>0.002307</v>
       </c>
       <c r="E133" s="9" t="n"/>
     </row>
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>22812.24</v>
+        <v>1535391.48</v>
       </c>
       <c r="D135" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>0.000149</v>
+        <v>0.01005</v>
       </c>
     </row>
     <row r="136">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>7174.49</v>
+        <v>1519753.73</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.314502</v>
+        <v>0.989815</v>
       </c>
       <c r="E137" s="9" t="n"/>
     </row>
@@ -3084,7 +3084,7 @@
         <v>15637.74</v>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.6854980000000001</v>
+        <v>0.010185</v>
       </c>
       <c r="E138" s="9" t="n"/>
     </row>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="C140" s="5" t="n">
-        <v>9546941.789999999</v>
+        <v>8445114.439999999</v>
       </c>
       <c r="D140" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>0.062488</v>
+        <v>0.055277</v>
       </c>
     </row>
     <row r="141">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>152779410.83</v>
+        <v>152779411.69</v>
       </c>
       <c r="D141" s="10" t="n"/>
       <c r="E141" s="12" t="n">

--- a/data/informes/cuadro_10_4.xlsx
+++ b/data/informes/cuadro_10_4.xlsx
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>35043831.29</v>
+        <v>34260361.36</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.229375</v>
+        <v>0.224247</v>
       </c>
     </row>
     <row r="5">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>34477521.72</v>
+        <v>33702713.49</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.98384</v>
+        <v>0.9837229999999999</v>
       </c>
       <c r="E5" s="9" t="n"/>
     </row>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>11723255.2</v>
+        <v>11105987.03</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.334531</v>
+        <v>0.324164</v>
       </c>
       <c r="E6" s="9" t="n"/>
     </row>
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>9809245.060000001</v>
+        <v>9246075.18</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.279914</v>
+        <v>0.269877</v>
       </c>
       <c r="E7" s="9" t="n"/>
     </row>
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>6758092.8</v>
+        <v>7575127.54</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.192847</v>
+        <v>0.221105</v>
       </c>
       <c r="E8" s="9" t="n"/>
     </row>
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>6166348.96</v>
+        <v>5754944.04</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.175961</v>
+        <v>0.167977</v>
       </c>
       <c r="E9" s="9" t="n"/>
     </row>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>560547.6899999999</v>
+        <v>551885.99</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.015996</v>
+        <v>0.016109</v>
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>560547.6899999999</v>
+        <v>551885.99</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.015996</v>
+        <v>0.016109</v>
       </c>
       <c r="E12" s="9" t="n"/>
     </row>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>33138329.57</v>
+        <v>38863878.47</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.216903</v>
+        <v>0.254379</v>
       </c>
     </row>
     <row r="14">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>32254651.81</v>
+        <v>37980200.71</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.9733339999999999</v>
+        <v>0.9772620000000001</v>
       </c>
       <c r="E14" s="9" t="n"/>
     </row>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>417203.58</v>
+        <v>480317.13</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.01259</v>
+        <v>0.012359</v>
       </c>
       <c r="E15" s="9" t="n"/>
     </row>
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>405761.08</v>
+        <v>475965.78</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.012244</v>
+        <v>0.012247</v>
       </c>
       <c r="E16" s="9" t="n"/>
     </row>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>804964.64</v>
+        <v>1005291.12</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.024291</v>
+        <v>0.025867</v>
       </c>
       <c r="E17" s="9" t="n"/>
     </row>
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>181469.16</v>
+        <v>188474.18</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.005476</v>
+        <v>0.00485</v>
       </c>
       <c r="E18" s="9" t="n"/>
     </row>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>69722.34</v>
+        <v>69722.33</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.002104</v>
+        <v>0.001794</v>
       </c>
       <c r="E19" s="9" t="n"/>
     </row>
@@ -830,7 +830,7 @@
         <v>34036.76</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.001027</v>
+        <v>0.0008759999999999999</v>
       </c>
       <c r="E20" s="9" t="n"/>
     </row>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>138363.23</v>
+        <v>174711.47</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.004175</v>
+        <v>0.004495</v>
       </c>
       <c r="E21" s="9" t="n"/>
     </row>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>325770.13</v>
+        <v>344592.69</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.009830999999999999</v>
+        <v>0.008867</v>
       </c>
       <c r="E22" s="9" t="n"/>
     </row>
@@ -884,10 +884,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>70286.75</v>
+        <v>119902.16</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.002121</v>
+        <v>0.003085</v>
       </c>
       <c r="E23" s="9" t="n"/>
     </row>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>1039308.13</v>
+        <v>1233473.13</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.031363</v>
+        <v>0.031738</v>
       </c>
       <c r="E24" s="9" t="n"/>
     </row>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>4661913.68</v>
+        <v>4703451.86</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.14068</v>
+        <v>0.121024</v>
       </c>
       <c r="E25" s="9" t="n"/>
     </row>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>3110514.18</v>
+        <v>3402437.02</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.093865</v>
+        <v>0.087548</v>
       </c>
       <c r="E26" s="9" t="n"/>
     </row>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>1663212.47</v>
+        <v>1670145.45</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.05019</v>
+        <v>0.042974</v>
       </c>
       <c r="E27" s="9" t="n"/>
     </row>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>1698668.23</v>
+        <v>1739543.23</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.05126</v>
+        <v>0.04476</v>
       </c>
       <c r="E28" s="9" t="n"/>
     </row>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>122497.25</v>
+        <v>159322.76</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.003697</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="E29" s="9" t="n"/>
     </row>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>135705.36</v>
+        <v>136740.07</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.004095</v>
+        <v>0.003518</v>
       </c>
       <c r="E30" s="9" t="n"/>
     </row>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>17375254.84</v>
+        <v>22042073.57</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.5243249999999999</v>
+        <v>0.567161</v>
       </c>
       <c r="E31" s="9" t="n"/>
     </row>
@@ -1096,7 +1096,7 @@
         <v>744905.22</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.022479</v>
+        <v>0.019167</v>
       </c>
       <c r="E34" s="9" t="n"/>
     </row>
@@ -1115,7 +1115,7 @@
         <v>138772.53</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.004188</v>
+        <v>0.003571</v>
       </c>
       <c r="E35" s="9" t="n"/>
     </row>
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>25376638.53</v>
+        <v>26003022.08</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.1661</v>
+        <v>0.1702</v>
       </c>
     </row>
     <row r="37">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>20940280.35</v>
+        <v>20760848.3</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.825179</v>
+        <v>0.798401</v>
       </c>
       <c r="E37" s="9" t="n"/>
     </row>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>514564.36</v>
+        <v>542608.73</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.020277</v>
+        <v>0.020867</v>
       </c>
       <c r="E38" s="9" t="n"/>
     </row>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>1710285.04</v>
+        <v>1703303.2</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.067396</v>
+        <v>0.06550399999999999</v>
       </c>
       <c r="E39" s="9" t="n"/>
     </row>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>561361.01</v>
+        <v>575145.95</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.022121</v>
+        <v>0.022118</v>
       </c>
       <c r="E40" s="9" t="n"/>
     </row>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>196964.18</v>
+        <v>179740.71</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.007762</v>
+        <v>0.006912000000000001</v>
       </c>
       <c r="E41" s="9" t="n"/>
     </row>
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>431095.58</v>
+        <v>431095.57</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.016988</v>
+        <v>0.016579</v>
       </c>
       <c r="E42" s="9" t="n"/>
     </row>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>758128.24</v>
+        <v>749271.24</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.029875</v>
+        <v>0.028815</v>
       </c>
       <c r="E43" s="9" t="n"/>
     </row>
@@ -1288,7 +1288,7 @@
         <v>543557.21</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.02142</v>
+        <v>0.020904</v>
       </c>
       <c r="E44" s="9" t="n"/>
     </row>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>333619.42</v>
+        <v>323031.85</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.013147</v>
+        <v>0.012423</v>
       </c>
       <c r="E45" s="9" t="n"/>
     </row>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>327822.12</v>
+        <v>306134.48</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.012918</v>
+        <v>0.011773</v>
       </c>
       <c r="E46" s="9" t="n"/>
     </row>
@@ -1345,7 +1345,7 @@
         <v>171152.2</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.006744</v>
+        <v>0.006582</v>
       </c>
       <c r="E47" s="9" t="n"/>
     </row>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>367394.48</v>
+        <v>351571.94</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.014478</v>
+        <v>0.01352</v>
       </c>
       <c r="E48" s="9" t="n"/>
     </row>
@@ -1383,7 +1383,7 @@
         <v>850744.66</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.033525</v>
+        <v>0.032717</v>
       </c>
       <c r="E49" s="9" t="n"/>
     </row>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>516192.08</v>
+        <v>493158.89</v>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.020341</v>
+        <v>0.018965</v>
       </c>
       <c r="E50" s="9" t="n"/>
     </row>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>1779349.1</v>
+        <v>1765654.46</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.070118</v>
+        <v>0.06790199999999999</v>
       </c>
       <c r="E51" s="9" t="n"/>
     </row>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>1928564.95</v>
+        <v>1925302.93</v>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.075998</v>
+        <v>0.074042</v>
       </c>
       <c r="E52" s="9" t="n"/>
     </row>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>593160.45</v>
+        <v>583383.7</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.023374</v>
+        <v>0.022435</v>
       </c>
       <c r="E53" s="9" t="n"/>
     </row>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>1543195.51</v>
+        <v>1544943.22</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.060812</v>
+        <v>0.05941399999999999</v>
       </c>
       <c r="E54" s="9" t="n"/>
     </row>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>737439.21</v>
+        <v>706112.53</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.02906</v>
+        <v>0.027155</v>
       </c>
       <c r="E55" s="9" t="n"/>
     </row>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>578464.98</v>
+        <v>564159.8199999999</v>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.022795</v>
+        <v>0.021696</v>
       </c>
       <c r="E56" s="9" t="n"/>
     </row>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>360358.1</v>
+        <v>356966.24</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.0142</v>
+        <v>0.013728</v>
       </c>
       <c r="E57" s="9" t="n"/>
     </row>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>1848553.75</v>
+        <v>1834548.44</v>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.07284500000000001</v>
+        <v>0.070551</v>
       </c>
       <c r="E58" s="9" t="n"/>
     </row>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>607723.89</v>
+        <v>593307.65</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.023948</v>
+        <v>0.022817</v>
       </c>
       <c r="E59" s="9" t="n"/>
     </row>
@@ -1592,7 +1592,7 @@
         <v>599582.1</v>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.023627</v>
+        <v>0.023058</v>
       </c>
       <c r="E60" s="9" t="n"/>
     </row>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>1492656.49</v>
+        <v>1478118.28</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.05882</v>
+        <v>0.056844</v>
       </c>
       <c r="E61" s="9" t="n"/>
     </row>
@@ -1630,7 +1630,7 @@
         <v>331900.3</v>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.013079</v>
+        <v>0.012764</v>
       </c>
       <c r="E62" s="9" t="n"/>
     </row>
@@ -1649,7 +1649,7 @@
         <v>151437.83</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.005968</v>
+        <v>0.005824</v>
       </c>
       <c r="E63" s="9" t="n"/>
     </row>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="C64" s="8" t="n">
-        <v>199035.85</v>
+        <v>198936.92</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.007842999999999999</v>
+        <v>0.007651</v>
       </c>
       <c r="E64" s="9" t="n"/>
     </row>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>905977.28</v>
+        <v>905977.27</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.035701</v>
+        <v>0.034841</v>
       </c>
       <c r="E65" s="9" t="n"/>
     </row>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="C66" s="8" t="n">
-        <v>4436358.18</v>
+        <v>5242173.78</v>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.174821</v>
+        <v>0.201599</v>
       </c>
       <c r="E66" s="9" t="n"/>
     </row>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>33056139.51</v>
+        <v>32962888.25</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>0.216365</v>
+        <v>0.215755</v>
       </c>
     </row>
     <row r="96">
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>1058971.57</v>
+        <v>1012827.67</v>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.032036</v>
+        <v>0.030726</v>
       </c>
       <c r="E96" s="9" t="n"/>
     </row>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>763077.3100000001</v>
+        <v>748640.0600000001</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.023084</v>
+        <v>0.022712</v>
       </c>
       <c r="E97" s="9" t="n"/>
     </row>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="C98" s="8" t="n">
-        <v>157645.66</v>
+        <v>157645.65</v>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.004769</v>
+        <v>0.004783</v>
       </c>
       <c r="E98" s="9" t="n"/>
     </row>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>101726.29</v>
+        <v>80467.31</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.003077</v>
+        <v>0.002441</v>
       </c>
       <c r="E99" s="9" t="n"/>
     </row>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="C100" s="8" t="n">
-        <v>36522.31</v>
+        <v>26074.65</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.001105</v>
+        <v>0.000791</v>
       </c>
       <c r="E100" s="9" t="n"/>
     </row>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>8646870.59</v>
+        <v>8620425.5</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.261581</v>
+        <v>0.261519</v>
       </c>
       <c r="E101" s="9" t="n"/>
     </row>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="C102" s="8" t="n">
-        <v>688643.96</v>
+        <v>667981.6899999999</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.020833</v>
+        <v>0.020265</v>
       </c>
       <c r="E102" s="9" t="n"/>
     </row>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>374923.69</v>
+        <v>354261.42</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.011342</v>
+        <v>0.010747</v>
       </c>
       <c r="E103" s="9" t="n"/>
     </row>
@@ -2434,7 +2434,7 @@
         <v>295706.8</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.008945999999999999</v>
+        <v>0.008971</v>
       </c>
       <c r="E104" s="9" t="n"/>
     </row>
@@ -2453,7 +2453,7 @@
         <v>18013.47</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.000545</v>
+        <v>0.000546</v>
       </c>
       <c r="E105" s="9" t="n"/>
     </row>
@@ -2472,7 +2472,7 @@
         <v>2111306.74</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.06387</v>
+        <v>0.064051</v>
       </c>
       <c r="E106" s="9" t="n"/>
     </row>
@@ -2491,7 +2491,7 @@
         <v>398388.1</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.012052</v>
+        <v>0.012086</v>
       </c>
       <c r="E107" s="9" t="n"/>
     </row>
@@ -2510,7 +2510,7 @@
         <v>293362.97</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.008874999999999999</v>
+        <v>0.0089</v>
       </c>
       <c r="E108" s="9" t="n"/>
     </row>
@@ -2529,7 +2529,7 @@
         <v>105025.14</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.003177</v>
+        <v>0.003186</v>
       </c>
       <c r="E109" s="9" t="n"/>
     </row>
@@ -2548,7 +2548,7 @@
         <v>6042348.45</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.182791</v>
+        <v>0.183308</v>
       </c>
       <c r="E110" s="9" t="n"/>
     </row>
@@ -2567,7 +2567,7 @@
         <v>680326.6899999999</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.020581</v>
+        <v>0.020639</v>
       </c>
       <c r="E111" s="9" t="n"/>
     </row>
@@ -2586,7 +2586,7 @@
         <v>288005.19</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.008713</v>
+        <v>0.008737</v>
       </c>
       <c r="E112" s="9" t="n"/>
     </row>
@@ -2605,7 +2605,7 @@
         <v>1113639.21</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.033689</v>
+        <v>0.033785</v>
       </c>
       <c r="E113" s="9" t="n"/>
     </row>
@@ -2624,7 +2624,7 @@
         <v>274474.32</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.008303</v>
+        <v>0.008326999999999999</v>
       </c>
       <c r="E114" s="9" t="n"/>
     </row>
@@ -2643,7 +2643,7 @@
         <v>1076083.54</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.032553</v>
+        <v>0.032645</v>
       </c>
       <c r="E115" s="9" t="n"/>
     </row>
@@ -2662,7 +2662,7 @@
         <v>1127119.4</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.034097</v>
+        <v>0.034194</v>
       </c>
       <c r="E116" s="9" t="n"/>
     </row>
@@ -2681,7 +2681,7 @@
         <v>138377.6</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.004186</v>
+        <v>0.004198</v>
       </c>
       <c r="E117" s="9" t="n"/>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1344322.5</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.040668</v>
+        <v>0.04078299999999999</v>
       </c>
       <c r="E118" s="9" t="n"/>
     </row>
@@ -2719,7 +2719,7 @@
         <v>14109610.09</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.426838</v>
+        <v>0.428045</v>
       </c>
       <c r="E119" s="9" t="n"/>
     </row>
@@ -2738,7 +2738,7 @@
         <v>2131582.51</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.064484</v>
+        <v>0.064666</v>
       </c>
       <c r="E120" s="9" t="n"/>
     </row>
@@ -2757,7 +2757,7 @@
         <v>1054468.78</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.031899</v>
+        <v>0.03199</v>
       </c>
       <c r="E121" s="9" t="n"/>
     </row>
@@ -2776,7 +2776,7 @@
         <v>89213.45</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.002699</v>
+        <v>0.002706</v>
       </c>
       <c r="E122" s="9" t="n"/>
     </row>
@@ -2795,7 +2795,7 @@
         <v>697637.97</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.021105</v>
+        <v>0.021164</v>
       </c>
       <c r="E123" s="9" t="n"/>
     </row>
@@ -2833,7 +2833,7 @@
         <v>2564834.08</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.07759000000000001</v>
+        <v>0.07780999999999999</v>
       </c>
       <c r="E125" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         <v>2374472.67</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.07183200000000001</v>
+        <v>0.072035</v>
       </c>
       <c r="E126" s="9" t="n"/>
     </row>
@@ -2871,7 +2871,7 @@
         <v>1485694.33</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.04494500000000001</v>
+        <v>0.045072</v>
       </c>
       <c r="E127" s="9" t="n"/>
     </row>
@@ -2890,7 +2890,7 @@
         <v>626217.8</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.018944</v>
+        <v>0.018998</v>
       </c>
       <c r="E128" s="9" t="n"/>
     </row>
@@ -2909,7 +2909,7 @@
         <v>469180.61</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.014193</v>
+        <v>0.014234</v>
       </c>
       <c r="E129" s="9" t="n"/>
     </row>
@@ -2928,7 +2928,7 @@
         <v>2005483.64</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.060669</v>
+        <v>0.06084100000000001</v>
       </c>
       <c r="E130" s="9" t="n"/>
     </row>
@@ -2947,7 +2947,7 @@
         <v>315644.06</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.009549</v>
+        <v>0.009575999999999999</v>
       </c>
       <c r="E131" s="9" t="n"/>
     </row>
@@ -2966,7 +2966,7 @@
         <v>218921.74</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.006623</v>
+        <v>0.006641</v>
       </c>
       <c r="E132" s="9" t="n"/>
     </row>
@@ -2985,7 +2985,7 @@
         <v>76258.46000000001</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.002307</v>
+        <v>0.002313</v>
       </c>
       <c r="E133" s="9" t="n"/>
     </row>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1535391.48</v>
+        <v>1535391.49</v>
       </c>
       <c r="D135" s="6" t="n">
         <v>1</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>1519753.73</v>
+        <v>1519753.74</v>
       </c>
       <c r="D137" s="9" t="n">
         <v>0.989815</v>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="C140" s="5" t="n">
-        <v>8445114.439999999</v>
+        <v>2969902.43</v>
       </c>
       <c r="D140" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>0.055277</v>
+        <v>0.019439</v>
       </c>
     </row>
     <row r="141">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>152779411.69</v>
+        <v>152779410.95</v>
       </c>
       <c r="D141" s="10" t="n"/>
       <c r="E141" s="12" t="n">

--- a/data/informes/cuadro_10_4.xlsx
+++ b/data/informes/cuadro_10_4.xlsx
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>34260361.36</v>
+        <v>45404907.34</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.224247</v>
+        <v>0.297612</v>
       </c>
     </row>
     <row r="5">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>33702713.49</v>
+        <v>44607339.77</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.9837229999999999</v>
+        <v>0.9824339999999999</v>
       </c>
       <c r="E5" s="9" t="n"/>
     </row>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>11105987.03</v>
+        <v>14265939.12</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.324164</v>
+        <v>0.314194</v>
       </c>
       <c r="E6" s="9" t="n"/>
     </row>
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>9246075.18</v>
+        <v>12380530.56</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.269877</v>
+        <v>0.272669</v>
       </c>
       <c r="E7" s="9" t="n"/>
     </row>
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>7575127.54</v>
+        <v>10182004.91</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.221105</v>
+        <v>0.224249</v>
       </c>
       <c r="E8" s="9" t="n"/>
     </row>
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>5754944.04</v>
+        <v>7748745.01</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.167977</v>
+        <v>0.170659</v>
       </c>
       <c r="E9" s="9" t="n"/>
     </row>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>551885.99</v>
+        <v>789134.53</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.016109</v>
+        <v>0.01738</v>
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>551885.99</v>
+        <v>789134.53</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.016109</v>
+        <v>0.01738</v>
       </c>
       <c r="E12" s="9" t="n"/>
     </row>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>38863878.47</v>
+        <v>64005462.29</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.254379</v>
+        <v>0.419532</v>
       </c>
     </row>
     <row r="14">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>37980200.71</v>
+        <v>62765645.71</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.9772620000000001</v>
+        <v>0.98063</v>
       </c>
       <c r="E14" s="9" t="n"/>
     </row>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>480317.13</v>
+        <v>666770.3199999999</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.012359</v>
+        <v>0.010417</v>
       </c>
       <c r="E15" s="9" t="n"/>
     </row>
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>475965.78</v>
+        <v>748168.53</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.012247</v>
+        <v>0.011689</v>
       </c>
       <c r="E16" s="9" t="n"/>
     </row>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1005291.12</v>
+        <v>1408329.43</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.025867</v>
+        <v>0.022003</v>
       </c>
       <c r="E17" s="9" t="n"/>
     </row>
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>188474.18</v>
+        <v>265472.58</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.00485</v>
+        <v>0.004148</v>
       </c>
       <c r="E18" s="9" t="n"/>
     </row>
@@ -811,7 +811,7 @@
         <v>69722.33</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.001794</v>
+        <v>0.001089</v>
       </c>
       <c r="E19" s="9" t="n"/>
     </row>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>34036.76</v>
+        <v>45426.29</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.0008759999999999999</v>
+        <v>0.0007099999999999999</v>
       </c>
       <c r="E20" s="9" t="n"/>
     </row>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>174711.47</v>
+        <v>280784.73</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.004495</v>
+        <v>0.004386999999999999</v>
       </c>
       <c r="E21" s="9" t="n"/>
     </row>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>344592.69</v>
+        <v>480668.26</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.008867</v>
+        <v>0.00751</v>
       </c>
       <c r="E22" s="9" t="n"/>
     </row>
@@ -884,10 +884,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>119902.16</v>
+        <v>157048.61</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.003085</v>
+        <v>0.002454</v>
       </c>
       <c r="E23" s="9" t="n"/>
     </row>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>1233473.13</v>
+        <v>1827099.23</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.031738</v>
+        <v>0.028546</v>
       </c>
       <c r="E24" s="9" t="n"/>
     </row>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>4703451.86</v>
+        <v>6831985.18</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.121024</v>
+        <v>0.106741</v>
       </c>
       <c r="E25" s="9" t="n"/>
     </row>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>3402437.02</v>
+        <v>5235735.76</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.087548</v>
+        <v>0.081801</v>
       </c>
       <c r="E26" s="9" t="n"/>
     </row>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>1670145.45</v>
+        <v>2227087.77</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.042974</v>
+        <v>0.034795</v>
       </c>
       <c r="E27" s="9" t="n"/>
     </row>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>1739543.23</v>
+        <v>2291377.35</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.04476</v>
+        <v>0.0358</v>
       </c>
       <c r="E28" s="9" t="n"/>
     </row>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>159322.76</v>
+        <v>252375.5</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.003942999999999999</v>
       </c>
       <c r="E29" s="9" t="n"/>
     </row>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>136740.07</v>
+        <v>184649.08</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.003518</v>
+        <v>0.002885</v>
       </c>
       <c r="E30" s="9" t="n"/>
     </row>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>22042073.57</v>
+        <v>39792944.75</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.567161</v>
+        <v>0.621712</v>
       </c>
       <c r="E31" s="9" t="n"/>
     </row>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>744905.22</v>
+        <v>1036710.65</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.019167</v>
+        <v>0.016197</v>
       </c>
       <c r="E34" s="9" t="n"/>
     </row>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>138772.53</v>
+        <v>203105.93</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.003571</v>
+        <v>0.003173</v>
       </c>
       <c r="E35" s="9" t="n"/>
     </row>
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>26003022.08</v>
+        <v>24212794.18</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.1702</v>
+        <v>0.158706</v>
       </c>
     </row>
     <row r="37">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>20760848.3</v>
+        <v>17442565.9</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.798401</v>
+        <v>0.720386</v>
       </c>
       <c r="E37" s="9" t="n"/>
     </row>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>542608.73</v>
+        <v>528051.64</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.020867</v>
+        <v>0.021809</v>
       </c>
       <c r="E38" s="9" t="n"/>
     </row>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>1703303.2</v>
+        <v>1201912.55</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.06550399999999999</v>
+        <v>0.04964</v>
       </c>
       <c r="E39" s="9" t="n"/>
     </row>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>575145.95</v>
+        <v>365806.83</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.022118</v>
+        <v>0.015108</v>
       </c>
       <c r="E40" s="9" t="n"/>
     </row>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>179740.71</v>
+        <v>150962.35</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.006912000000000001</v>
+        <v>0.006235000000000001</v>
       </c>
       <c r="E41" s="9" t="n"/>
     </row>
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>431095.57</v>
+        <v>402000.21</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.016579</v>
+        <v>0.016603</v>
       </c>
       <c r="E42" s="9" t="n"/>
     </row>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>749271.24</v>
+        <v>754260.97</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.028815</v>
+        <v>0.031151</v>
       </c>
       <c r="E43" s="9" t="n"/>
     </row>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>543557.21</v>
+        <v>434484.9</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.020904</v>
+        <v>0.017944</v>
       </c>
       <c r="E44" s="9" t="n"/>
     </row>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>323031.85</v>
+        <v>303003.68</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.012423</v>
+        <v>0.012514</v>
       </c>
       <c r="E45" s="9" t="n"/>
     </row>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>306134.48</v>
+        <v>253181.26</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.011773</v>
+        <v>0.010457</v>
       </c>
       <c r="E46" s="9" t="n"/>
     </row>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>171152.2</v>
+        <v>176483.51</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.006582</v>
+        <v>0.007289</v>
       </c>
       <c r="E47" s="9" t="n"/>
     </row>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>351571.94</v>
+        <v>379694.26</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.01352</v>
+        <v>0.015682</v>
       </c>
       <c r="E48" s="9" t="n"/>
     </row>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>850744.66</v>
+        <v>643373.0699999999</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.032717</v>
+        <v>0.026572</v>
       </c>
       <c r="E49" s="9" t="n"/>
     </row>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>493158.89</v>
+        <v>416074.29</v>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.018965</v>
+        <v>0.017184</v>
       </c>
       <c r="E50" s="9" t="n"/>
     </row>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>1765654.46</v>
+        <v>1947433.04</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.06790199999999999</v>
+        <v>0.08042999999999999</v>
       </c>
       <c r="E51" s="9" t="n"/>
     </row>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>1925302.93</v>
+        <v>1424067.79</v>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.074042</v>
+        <v>0.058815</v>
       </c>
       <c r="E52" s="9" t="n"/>
     </row>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>583383.7</v>
+        <v>578698.92</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.022435</v>
+        <v>0.023901</v>
       </c>
       <c r="E53" s="9" t="n"/>
     </row>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>1544943.22</v>
+        <v>1544576.76</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.05941399999999999</v>
+        <v>0.063792</v>
       </c>
       <c r="E54" s="9" t="n"/>
     </row>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>706112.53</v>
+        <v>482044.6</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.027155</v>
+        <v>0.019909</v>
       </c>
       <c r="E55" s="9" t="n"/>
     </row>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>564159.8199999999</v>
+        <v>520864.25</v>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.021696</v>
+        <v>0.021512</v>
       </c>
       <c r="E56" s="9" t="n"/>
     </row>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>356966.24</v>
+        <v>308642.3</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.013728</v>
+        <v>0.012747</v>
       </c>
       <c r="E57" s="9" t="n"/>
     </row>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>1834548.44</v>
+        <v>1398662.63</v>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.070551</v>
+        <v>0.057765</v>
       </c>
       <c r="E58" s="9" t="n"/>
     </row>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>593307.65</v>
+        <v>394932.23</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.022817</v>
+        <v>0.016311</v>
       </c>
       <c r="E59" s="9" t="n"/>
     </row>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="C60" s="8" t="n">
-        <v>599582.1</v>
+        <v>592904.38</v>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.023058</v>
+        <v>0.024487</v>
       </c>
       <c r="E60" s="9" t="n"/>
     </row>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>1478118.28</v>
+        <v>890238.92</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.056844</v>
+        <v>0.036767</v>
       </c>
       <c r="E61" s="9" t="n"/>
     </row>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>331900.3</v>
+        <v>357824.61</v>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.012764</v>
+        <v>0.014778</v>
       </c>
       <c r="E62" s="9" t="n"/>
     </row>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>151437.83</v>
+        <v>136473.49</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.005824</v>
+        <v>0.005636</v>
       </c>
       <c r="E63" s="9" t="n"/>
     </row>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="C64" s="8" t="n">
-        <v>198936.92</v>
+        <v>224281.04</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.007651</v>
+        <v>0.009263</v>
       </c>
       <c r="E64" s="9" t="n"/>
     </row>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>905977.27</v>
+        <v>631631.42</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.034841</v>
+        <v>0.026087</v>
       </c>
       <c r="E65" s="9" t="n"/>
     </row>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="C66" s="8" t="n">
-        <v>5242173.78</v>
+        <v>6770228.28</v>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.201599</v>
+        <v>0.279614</v>
       </c>
       <c r="E66" s="9" t="n"/>
     </row>
@@ -1760,13 +1760,13 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>10896354.82</v>
+        <v>968229.6800000001</v>
       </c>
       <c r="D69" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>0.07132100000000001</v>
+        <v>0.006346000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="C70" s="8" t="n">
-        <v>2524954.68</v>
+        <v>0</v>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.231725</v>
+        <v>0</v>
       </c>
       <c r="E70" s="9" t="n"/>
     </row>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>4009694.33</v>
+        <v>719051.78</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.367985</v>
+        <v>0.742646</v>
       </c>
       <c r="E71" s="9" t="n"/>
     </row>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="C72" s="8" t="n">
-        <v>410808.75</v>
+        <v>933.01</v>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.037701</v>
+        <v>0.000964</v>
       </c>
       <c r="E72" s="9" t="n"/>
     </row>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>290168.86</v>
+        <v>0</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.02663</v>
+        <v>0</v>
       </c>
       <c r="E73" s="9" t="n"/>
     </row>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="C74" s="8" t="n">
-        <v>1137344.84</v>
+        <v>0</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.104378</v>
+        <v>0</v>
       </c>
       <c r="E74" s="9" t="n"/>
     </row>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>806019.05</v>
+        <v>368074.51</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.073971</v>
+        <v>0.380152</v>
       </c>
       <c r="E75" s="9" t="n"/>
     </row>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="C76" s="8" t="n">
-        <v>776947.77</v>
+        <v>337676.93</v>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.07130300000000001</v>
+        <v>0.348757</v>
       </c>
       <c r="E76" s="9" t="n"/>
     </row>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>345873.09</v>
+        <v>0</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.031742</v>
+        <v>0</v>
       </c>
       <c r="E77" s="9" t="n"/>
     </row>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="C78" s="8" t="n">
-        <v>242531.97</v>
+        <v>12367.33</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.022258</v>
+        <v>0.012773</v>
       </c>
       <c r="E78" s="9" t="n"/>
     </row>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>3855737.54</v>
+        <v>234607.29</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.3538559999999999</v>
+        <v>0.242305</v>
       </c>
       <c r="E79" s="9" t="n"/>
     </row>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="C80" s="8" t="n">
-        <v>1927287.27</v>
+        <v>0</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.176874</v>
+        <v>0</v>
       </c>
       <c r="E80" s="9" t="n"/>
     </row>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>1488552.09</v>
+        <v>153348.99</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.13661</v>
+        <v>0.158381</v>
       </c>
       <c r="E81" s="9" t="n"/>
     </row>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>439898.18</v>
+        <v>81258.3</v>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.040371</v>
+        <v>0.083925</v>
       </c>
       <c r="E82" s="9" t="n"/>
     </row>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>505968.27</v>
+        <v>14570.6</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.046435</v>
+        <v>0.015049</v>
       </c>
       <c r="E83" s="9" t="n"/>
     </row>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="C86" s="8" t="n">
-        <v>408873.43</v>
+        <v>14570.6</v>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.037524</v>
+        <v>0.015049</v>
       </c>
       <c r="E86" s="9" t="n"/>
     </row>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>51418.56</v>
+        <v>0</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.004719</v>
+        <v>0</v>
       </c>
       <c r="E87" s="9" t="n"/>
     </row>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="C88" s="8" t="n">
-        <v>45676.28</v>
+        <v>0</v>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.004192</v>
+        <v>0</v>
       </c>
       <c r="E88" s="9" t="n"/>
     </row>
@@ -2142,13 +2142,13 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>5150926.76</v>
+        <v>6464822.47</v>
       </c>
       <c r="D89" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>0.033715</v>
+        <v>0.042375</v>
       </c>
     </row>
     <row r="90">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="C90" s="8" t="n">
-        <v>1501527.08</v>
+        <v>1919731.65</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.291506</v>
+        <v>0.29695</v>
       </c>
       <c r="E90" s="9" t="n"/>
     </row>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>3061799.43</v>
+        <v>3750494.97</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.594417</v>
+        <v>0.580139</v>
       </c>
       <c r="E91" s="9" t="n"/>
     </row>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>459289.82</v>
+        <v>627906.12</v>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.08916600000000001</v>
+        <v>0.097127</v>
       </c>
       <c r="E92" s="9" t="n"/>
     </row>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="C94" s="8" t="n">
-        <v>45523.13</v>
+        <v>45523.14</v>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.008838</v>
+        <v>0.007042000000000001</v>
       </c>
       <c r="E94" s="9" t="n"/>
     </row>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>32962888.25</v>
+        <v>8445622.01</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>0.215755</v>
+        <v>0.055358</v>
       </c>
     </row>
     <row r="96">
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>1012827.67</v>
+        <v>0</v>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.030726</v>
+        <v>0</v>
       </c>
       <c r="E96" s="9" t="n"/>
     </row>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>748640.0600000001</v>
+        <v>0</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.022712</v>
+        <v>0</v>
       </c>
       <c r="E97" s="9" t="n"/>
     </row>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="C98" s="8" t="n">
-        <v>157645.65</v>
+        <v>0</v>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.004783</v>
+        <v>0</v>
       </c>
       <c r="E98" s="9" t="n"/>
     </row>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>80467.31</v>
+        <v>0</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.002441</v>
+        <v>0</v>
       </c>
       <c r="E99" s="9" t="n"/>
     </row>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="C100" s="8" t="n">
-        <v>26074.65</v>
+        <v>0</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.000791</v>
+        <v>0</v>
       </c>
       <c r="E100" s="9" t="n"/>
     </row>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>8620425.5</v>
+        <v>5952836.57</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.261519</v>
+        <v>0.704843</v>
       </c>
       <c r="E101" s="9" t="n"/>
     </row>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="C102" s="8" t="n">
-        <v>667981.6899999999</v>
+        <v>0</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.020265</v>
+        <v>0</v>
       </c>
       <c r="E102" s="9" t="n"/>
     </row>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>354261.42</v>
+        <v>0</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.010747</v>
+        <v>0</v>
       </c>
       <c r="E103" s="9" t="n"/>
     </row>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="C104" s="8" t="n">
-        <v>295706.8</v>
+        <v>0</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.008971</v>
+        <v>0</v>
       </c>
       <c r="E104" s="9" t="n"/>
     </row>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>18013.47</v>
+        <v>0</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.000546</v>
+        <v>0</v>
       </c>
       <c r="E105" s="9" t="n"/>
     </row>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="C106" s="8" t="n">
-        <v>2111306.74</v>
+        <v>311416.63</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.064051</v>
+        <v>0.036873</v>
       </c>
       <c r="E106" s="9" t="n"/>
     </row>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>398388.1</v>
+        <v>38053.31</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.012086</v>
+        <v>0.004506</v>
       </c>
       <c r="E107" s="9" t="n"/>
     </row>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="C108" s="8" t="n">
-        <v>293362.97</v>
+        <v>38053.31</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.0089</v>
+        <v>0.004506</v>
       </c>
       <c r="E108" s="9" t="n"/>
     </row>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>105025.14</v>
+        <v>0</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.003186</v>
+        <v>0</v>
       </c>
       <c r="E109" s="9" t="n"/>
     </row>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="C110" s="8" t="n">
-        <v>6042348.45</v>
+        <v>0</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.183308</v>
+        <v>0</v>
       </c>
       <c r="E110" s="9" t="n"/>
     </row>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>680326.6899999999</v>
+        <v>0</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.020639</v>
+        <v>0</v>
       </c>
       <c r="E111" s="9" t="n"/>
     </row>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="C112" s="8" t="n">
-        <v>288005.19</v>
+        <v>0</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.008737</v>
+        <v>0</v>
       </c>
       <c r="E112" s="9" t="n"/>
     </row>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>1113639.21</v>
+        <v>0</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.033785</v>
+        <v>0</v>
       </c>
       <c r="E113" s="9" t="n"/>
     </row>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="C114" s="8" t="n">
-        <v>274474.32</v>
+        <v>0</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.008326999999999999</v>
+        <v>0</v>
       </c>
       <c r="E114" s="9" t="n"/>
     </row>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>1076083.54</v>
+        <v>0</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.032645</v>
+        <v>0</v>
       </c>
       <c r="E115" s="9" t="n"/>
     </row>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="C116" s="8" t="n">
-        <v>1127119.4</v>
+        <v>0</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.034194</v>
+        <v>0</v>
       </c>
       <c r="E116" s="9" t="n"/>
     </row>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>138377.6</v>
+        <v>0</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.004198</v>
+        <v>0</v>
       </c>
       <c r="E117" s="9" t="n"/>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="C118" s="8" t="n">
-        <v>1344322.5</v>
+        <v>0</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.04078299999999999</v>
+        <v>0</v>
       </c>
       <c r="E118" s="9" t="n"/>
     </row>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>14109610.09</v>
+        <v>2143315.5</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.428045</v>
+        <v>0.253778</v>
       </c>
       <c r="E119" s="9" t="n"/>
     </row>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="C120" s="8" t="n">
-        <v>2131582.51</v>
+        <v>0</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.064666</v>
+        <v>0</v>
       </c>
       <c r="E120" s="9" t="n"/>
     </row>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>1054468.78</v>
+        <v>94937.73</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.03199</v>
+        <v>0.011241</v>
       </c>
       <c r="E121" s="9" t="n"/>
     </row>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="C122" s="8" t="n">
-        <v>89213.45</v>
+        <v>0</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.002706</v>
+        <v>0</v>
       </c>
       <c r="E122" s="9" t="n"/>
     </row>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>697637.97</v>
+        <v>0</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.021164</v>
+        <v>0</v>
       </c>
       <c r="E123" s="9" t="n"/>
     </row>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>2564834.08</v>
+        <v>0</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.07780999999999999</v>
+        <v>0</v>
       </c>
       <c r="E125" s="9" t="n"/>
     </row>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="C126" s="8" t="n">
-        <v>2374472.67</v>
+        <v>0</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.072035</v>
+        <v>0</v>
       </c>
       <c r="E126" s="9" t="n"/>
     </row>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>1485694.33</v>
+        <v>0</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.045072</v>
+        <v>0</v>
       </c>
       <c r="E127" s="9" t="n"/>
     </row>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="C128" s="8" t="n">
-        <v>626217.8</v>
+        <v>0</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.018998</v>
+        <v>0</v>
       </c>
       <c r="E128" s="9" t="n"/>
     </row>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>469180.61</v>
+        <v>0</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.014234</v>
+        <v>0</v>
       </c>
       <c r="E129" s="9" t="n"/>
     </row>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="C130" s="8" t="n">
-        <v>2005483.64</v>
+        <v>2048377.76</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.06084100000000001</v>
+        <v>0.242537</v>
       </c>
       <c r="E130" s="9" t="n"/>
     </row>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>315644.06</v>
+        <v>0</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.009575999999999999</v>
+        <v>0</v>
       </c>
       <c r="E131" s="9" t="n"/>
     </row>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="C132" s="8" t="n">
-        <v>218921.74</v>
+        <v>0</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.006641</v>
+        <v>0</v>
       </c>
       <c r="E132" s="9" t="n"/>
     </row>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>76258.46000000001</v>
+        <v>0</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.002313</v>
+        <v>0</v>
       </c>
       <c r="E133" s="9" t="n"/>
     </row>
@@ -3001,13 +3001,13 @@
         </is>
       </c>
       <c r="C134" s="5" t="n">
-        <v>136685.3</v>
+        <v>0</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>0.000895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1535391.49</v>
+        <v>1508929.53</v>
       </c>
       <c r="D135" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>0.01005</v>
+        <v>0.009889999999999999</v>
       </c>
     </row>
     <row r="136">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>1519753.74</v>
+        <v>1508929.53</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.989815</v>
+        <v>1</v>
       </c>
       <c r="E137" s="9" t="n"/>
     </row>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="C138" s="8" t="n">
-        <v>15637.74</v>
+        <v>0</v>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.010185</v>
+        <v>0</v>
       </c>
       <c r="E138" s="9" t="n"/>
     </row>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="C140" s="5" t="n">
-        <v>2969902.43</v>
+        <v>1553182.89</v>
       </c>
       <c r="D140" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>0.019439</v>
+        <v>0.010181</v>
       </c>
     </row>
     <row r="141">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>152779410.95</v>
+        <v>152563950.4</v>
       </c>
       <c r="D141" s="10" t="n"/>
       <c r="E141" s="12" t="n">

--- a/data/informes/cuadro_10_4.xlsx
+++ b/data/informes/cuadro_10_4.xlsx
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>45404907.34</v>
+        <v>44116686.04</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.297612</v>
+        <v>0.289168</v>
       </c>
     </row>
     <row r="5">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>44607339.77</v>
+        <v>43344452.16</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.9824339999999999</v>
+        <v>0.982496</v>
       </c>
       <c r="E5" s="9" t="n"/>
     </row>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>14265939.12</v>
+        <v>13448114.45</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.314194</v>
+        <v>0.304831</v>
       </c>
       <c r="E6" s="9" t="n"/>
     </row>
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>12380530.56</v>
+        <v>12192854.28</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.272669</v>
+        <v>0.276377</v>
       </c>
       <c r="E7" s="9" t="n"/>
     </row>
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>10182004.91</v>
+        <v>9926251.35</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.224249</v>
+        <v>0.225</v>
       </c>
       <c r="E8" s="9" t="n"/>
     </row>
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>7748745.01</v>
+        <v>7747720.95</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.170659</v>
+        <v>0.175619</v>
       </c>
       <c r="E9" s="9" t="n"/>
     </row>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>789134.53</v>
+        <v>763971.37</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.01738</v>
+        <v>0.017317</v>
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>789134.53</v>
+        <v>763971.37</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.01738</v>
+        <v>0.017317</v>
       </c>
       <c r="E12" s="9" t="n"/>
     </row>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>64005462.29</v>
+        <v>65298325.24</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.419532</v>
+        <v>0.4280060000000001</v>
       </c>
     </row>
     <row r="14">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>62765645.71</v>
+        <v>64081763.57</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.98063</v>
+        <v>0.9813689999999999</v>
       </c>
       <c r="E14" s="9" t="n"/>
     </row>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>666770.3199999999</v>
+        <v>673601.35</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.010417</v>
+        <v>0.010316</v>
       </c>
       <c r="E15" s="9" t="n"/>
     </row>
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>748168.53</v>
+        <v>775238.16</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.011689</v>
+        <v>0.011872</v>
       </c>
       <c r="E16" s="9" t="n"/>
     </row>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1408329.43</v>
+        <v>1451832.52</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.022003</v>
+        <v>0.022234</v>
       </c>
       <c r="E17" s="9" t="n"/>
     </row>
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>265472.58</v>
+        <v>273494.98</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.004148</v>
+        <v>0.004188</v>
       </c>
       <c r="E18" s="9" t="n"/>
     </row>
@@ -811,7 +811,7 @@
         <v>69722.33</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.001089</v>
+        <v>0.001068</v>
       </c>
       <c r="E19" s="9" t="n"/>
     </row>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>45426.29</v>
+        <v>45966.01</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.0007099999999999999</v>
+        <v>0.0007040000000000001</v>
       </c>
       <c r="E20" s="9" t="n"/>
     </row>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>280784.73</v>
+        <v>281652.05</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.004386999999999999</v>
+        <v>0.004313</v>
       </c>
       <c r="E21" s="9" t="n"/>
     </row>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>480668.26</v>
+        <v>495607.62</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.00751</v>
+        <v>0.00759</v>
       </c>
       <c r="E22" s="9" t="n"/>
     </row>
@@ -884,10 +884,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>157048.61</v>
+        <v>157919.23</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.002454</v>
+        <v>0.002418</v>
       </c>
       <c r="E23" s="9" t="n"/>
     </row>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>1827099.23</v>
+        <v>1888008.69</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.028546</v>
+        <v>0.028914</v>
       </c>
       <c r="E24" s="9" t="n"/>
     </row>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>6831985.18</v>
+        <v>6961520.04</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.106741</v>
+        <v>0.106611</v>
       </c>
       <c r="E25" s="9" t="n"/>
     </row>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>5235735.76</v>
+        <v>5372339.32</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.081801</v>
+        <v>0.082274</v>
       </c>
       <c r="E26" s="9" t="n"/>
     </row>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>2227087.77</v>
+        <v>2210114.43</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.034795</v>
+        <v>0.033846</v>
       </c>
       <c r="E27" s="9" t="n"/>
     </row>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>2291377.35</v>
+        <v>1940901.07</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.0358</v>
+        <v>0.029724</v>
       </c>
       <c r="E28" s="9" t="n"/>
     </row>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>252375.5</v>
+        <v>258834.04</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.003942999999999999</v>
+        <v>0.003964</v>
       </c>
       <c r="E29" s="9" t="n"/>
     </row>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>184649.08</v>
+        <v>156078.82</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.002885</v>
+        <v>0.00239</v>
       </c>
       <c r="E30" s="9" t="n"/>
     </row>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>39792944.75</v>
+        <v>41068932.91</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.621712</v>
+        <v>0.628943</v>
       </c>
       <c r="E31" s="9" t="n"/>
     </row>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>1036710.65</v>
+        <v>1005577.74</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.016197</v>
+        <v>0.0154</v>
       </c>
       <c r="E34" s="9" t="n"/>
     </row>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>203105.93</v>
+        <v>210983.93</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.003173</v>
+        <v>0.003231</v>
       </c>
       <c r="E35" s="9" t="n"/>
     </row>
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>24212794.18</v>
+        <v>22346700.44</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.158706</v>
+        <v>0.146474</v>
       </c>
     </row>
     <row r="37">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>17442565.9</v>
+        <v>15538027.33</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.720386</v>
+        <v>0.6953159999999999</v>
       </c>
       <c r="E37" s="9" t="n"/>
     </row>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>528051.64</v>
+        <v>457438.3</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.021809</v>
+        <v>0.02047</v>
       </c>
       <c r="E38" s="9" t="n"/>
     </row>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>1201912.55</v>
+        <v>1064763.24</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.04964</v>
+        <v>0.047647</v>
       </c>
       <c r="E39" s="9" t="n"/>
     </row>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>365806.83</v>
+        <v>316293.39</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.015108</v>
+        <v>0.014154</v>
       </c>
       <c r="E40" s="9" t="n"/>
     </row>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>150962.35</v>
+        <v>110774.26</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.006235000000000001</v>
+        <v>0.004957</v>
       </c>
       <c r="E41" s="9" t="n"/>
     </row>
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>402000.21</v>
+        <v>304047.3</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.016603</v>
+        <v>0.013606</v>
       </c>
       <c r="E42" s="9" t="n"/>
     </row>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>754260.97</v>
+        <v>673147.0699999999</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.031151</v>
+        <v>0.030123</v>
       </c>
       <c r="E43" s="9" t="n"/>
     </row>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>434484.9</v>
+        <v>161242.21</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.017944</v>
+        <v>0.007215</v>
       </c>
       <c r="E44" s="9" t="n"/>
     </row>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>303003.68</v>
+        <v>437068.08</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.012514</v>
+        <v>0.019559</v>
       </c>
       <c r="E45" s="9" t="n"/>
     </row>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>253181.26</v>
+        <v>209289.82</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.010457</v>
+        <v>0.009365999999999999</v>
       </c>
       <c r="E46" s="9" t="n"/>
     </row>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>176483.51</v>
+        <v>156344.94</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.007289</v>
+        <v>0.006996</v>
       </c>
       <c r="E47" s="9" t="n"/>
     </row>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>379694.26</v>
+        <v>306867.68</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.015682</v>
+        <v>0.013732</v>
       </c>
       <c r="E48" s="9" t="n"/>
     </row>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>643373.0699999999</v>
+        <v>586672.96</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.026572</v>
+        <v>0.026253</v>
       </c>
       <c r="E49" s="9" t="n"/>
     </row>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>416074.29</v>
+        <v>364871.41</v>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.017184</v>
+        <v>0.016328</v>
       </c>
       <c r="E50" s="9" t="n"/>
     </row>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>1947433.04</v>
+        <v>1782106.91</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.08042999999999999</v>
+        <v>0.079748</v>
       </c>
       <c r="E51" s="9" t="n"/>
     </row>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>1424067.79</v>
+        <v>1182295.25</v>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.058815</v>
+        <v>0.052907</v>
       </c>
       <c r="E52" s="9" t="n"/>
     </row>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>578698.92</v>
+        <v>528667.15</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.023901</v>
+        <v>0.023658</v>
       </c>
       <c r="E53" s="9" t="n"/>
     </row>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>1544576.76</v>
+        <v>1470919.81</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.063792</v>
+        <v>0.06582300000000001</v>
       </c>
       <c r="E54" s="9" t="n"/>
     </row>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>482044.6</v>
+        <v>414126.09</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.019909</v>
+        <v>0.018532</v>
       </c>
       <c r="E55" s="9" t="n"/>
     </row>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>520864.25</v>
+        <v>435500.93</v>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.021512</v>
+        <v>0.019488</v>
       </c>
       <c r="E56" s="9" t="n"/>
     </row>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>308642.3</v>
+        <v>276477.89</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.012747</v>
+        <v>0.012372</v>
       </c>
       <c r="E57" s="9" t="n"/>
     </row>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>1398662.63</v>
+        <v>1383529.14</v>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.057765</v>
+        <v>0.061912</v>
       </c>
       <c r="E58" s="9" t="n"/>
     </row>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>394932.23</v>
+        <v>384103.02</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.016311</v>
+        <v>0.017188</v>
       </c>
       <c r="E59" s="9" t="n"/>
     </row>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="C60" s="8" t="n">
-        <v>592904.38</v>
+        <v>516302.8</v>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.024487</v>
+        <v>0.023104</v>
       </c>
       <c r="E60" s="9" t="n"/>
     </row>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>890238.92</v>
+        <v>816602.62</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.036767</v>
+        <v>0.036542</v>
       </c>
       <c r="E61" s="9" t="n"/>
     </row>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>357824.61</v>
+        <v>308711.13</v>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.014778</v>
+        <v>0.013815</v>
       </c>
       <c r="E62" s="9" t="n"/>
     </row>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>136473.49</v>
+        <v>96448.96000000001</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.005636</v>
+        <v>0.004316</v>
       </c>
       <c r="E63" s="9" t="n"/>
     </row>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="C64" s="8" t="n">
-        <v>224281.04</v>
+        <v>200961.32</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.009263</v>
+        <v>0.008992999999999999</v>
       </c>
       <c r="E64" s="9" t="n"/>
     </row>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>631631.42</v>
+        <v>592453.64</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.026087</v>
+        <v>0.026512</v>
       </c>
       <c r="E65" s="9" t="n"/>
     </row>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="C66" s="8" t="n">
-        <v>6770228.28</v>
+        <v>6808673.12</v>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.279614</v>
+        <v>0.304684</v>
       </c>
       <c r="E66" s="9" t="n"/>
     </row>
@@ -1760,13 +1760,13 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>968229.6800000001</v>
+        <v>2603348.33</v>
       </c>
       <c r="D69" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>0.006346000000000001</v>
+        <v>0.017064</v>
       </c>
     </row>
     <row r="70">
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="C70" s="8" t="n">
-        <v>0</v>
+        <v>39322.9</v>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0</v>
+        <v>0.015105</v>
       </c>
       <c r="E70" s="9" t="n"/>
     </row>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>719051.78</v>
+        <v>717102.83</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.742646</v>
+        <v>0.275454</v>
       </c>
       <c r="E71" s="9" t="n"/>
     </row>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="C72" s="8" t="n">
-        <v>933.01</v>
+        <v>7940.29</v>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.000964</v>
+        <v>0.00305</v>
       </c>
       <c r="E72" s="9" t="n"/>
     </row>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>0</v>
+        <v>723.67</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0</v>
+        <v>0.000278</v>
       </c>
       <c r="E73" s="9" t="n"/>
     </row>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="C74" s="8" t="n">
-        <v>0</v>
+        <v>3560.1</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0</v>
+        <v>0.001368</v>
       </c>
       <c r="E74" s="9" t="n"/>
     </row>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>368074.51</v>
+        <v>361721.48</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.380152</v>
+        <v>0.138945</v>
       </c>
       <c r="E75" s="9" t="n"/>
     </row>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="C76" s="8" t="n">
-        <v>337676.93</v>
+        <v>329957.69</v>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.348757</v>
+        <v>0.126744</v>
       </c>
       <c r="E76" s="9" t="n"/>
     </row>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>0</v>
+        <v>753.9299999999999</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0</v>
+        <v>0.00029</v>
       </c>
       <c r="E77" s="9" t="n"/>
     </row>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="C78" s="8" t="n">
-        <v>12367.33</v>
+        <v>12445.67</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.012773</v>
+        <v>0.004781000000000001</v>
       </c>
       <c r="E78" s="9" t="n"/>
     </row>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>234607.29</v>
+        <v>1734239.61</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.242305</v>
+        <v>0.666157</v>
       </c>
       <c r="E79" s="9" t="n"/>
     </row>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="C80" s="8" t="n">
-        <v>0</v>
+        <v>9365.389999999999</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0</v>
+        <v>0.003597</v>
       </c>
       <c r="E80" s="9" t="n"/>
     </row>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>153348.99</v>
+        <v>1429207.85</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.158381</v>
+        <v>0.548988</v>
       </c>
       <c r="E81" s="9" t="n"/>
     </row>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>81258.3</v>
+        <v>295666.37</v>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.083925</v>
+        <v>0.113572</v>
       </c>
       <c r="E82" s="9" t="n"/>
     </row>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>14570.6</v>
+        <v>112682.99</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.015049</v>
+        <v>0.043284</v>
       </c>
       <c r="E83" s="9" t="n"/>
     </row>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="C86" s="8" t="n">
-        <v>14570.6</v>
+        <v>60456.79</v>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.015049</v>
+        <v>0.023223</v>
       </c>
       <c r="E86" s="9" t="n"/>
     </row>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>0</v>
+        <v>51418.56</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0</v>
+        <v>0.019751</v>
       </c>
       <c r="E87" s="9" t="n"/>
     </row>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="C88" s="8" t="n">
-        <v>0</v>
+        <v>807.64</v>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0</v>
+        <v>0.00031</v>
       </c>
       <c r="E88" s="9" t="n"/>
     </row>
@@ -2142,13 +2142,13 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>6464822.47</v>
+        <v>4572140.75</v>
       </c>
       <c r="D89" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>0.042375</v>
+        <v>0.029969</v>
       </c>
     </row>
     <row r="90">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="C90" s="8" t="n">
-        <v>1919731.65</v>
+        <v>1414702.44</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.29695</v>
+        <v>0.309418</v>
       </c>
       <c r="E90" s="9" t="n"/>
     </row>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>3750494.97</v>
+        <v>2390006.49</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.580139</v>
+        <v>0.522732</v>
       </c>
       <c r="E91" s="9" t="n"/>
     </row>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>627906.12</v>
+        <v>605336.4</v>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.097127</v>
+        <v>0.132397</v>
       </c>
       <c r="E92" s="9" t="n"/>
     </row>
@@ -2242,7 +2242,7 @@
         <v>45523.14</v>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.007042000000000001</v>
+        <v>0.009957000000000001</v>
       </c>
       <c r="E94" s="9" t="n"/>
     </row>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>8445622.01</v>
+        <v>10201156.61</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>0.055358</v>
+        <v>0.06686499999999999</v>
       </c>
     </row>
     <row r="96">
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>0</v>
+        <v>73023.05</v>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0</v>
+        <v>0.007158</v>
       </c>
       <c r="E96" s="9" t="n"/>
     </row>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>0</v>
+        <v>72220.78999999999</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0</v>
+        <v>0.007079999999999999</v>
       </c>
       <c r="E97" s="9" t="n"/>
     </row>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>0</v>
+        <v>467.75</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0</v>
+        <v>4.6e-05</v>
       </c>
       <c r="E99" s="9" t="n"/>
     </row>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="C100" s="8" t="n">
-        <v>0</v>
+        <v>334.51</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0</v>
+        <v>3.3e-05</v>
       </c>
       <c r="E100" s="9" t="n"/>
     </row>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>5952836.57</v>
+        <v>6336981.46</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.704843</v>
+        <v>0.6212019999999999</v>
       </c>
       <c r="E101" s="9" t="n"/>
     </row>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="C102" s="8" t="n">
-        <v>0</v>
+        <v>4936.7</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0</v>
+        <v>0.000484</v>
       </c>
       <c r="E102" s="9" t="n"/>
     </row>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>0</v>
+        <v>3129.05</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0</v>
+        <v>0.000307</v>
       </c>
       <c r="E103" s="9" t="n"/>
     </row>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="C104" s="8" t="n">
-        <v>0</v>
+        <v>1038.52</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0</v>
+        <v>0.000102</v>
       </c>
       <c r="E104" s="9" t="n"/>
     </row>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>0</v>
+        <v>769.12</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0</v>
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="E105" s="9" t="n"/>
     </row>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="C106" s="8" t="n">
-        <v>311416.63</v>
+        <v>1211124.17</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.036873</v>
+        <v>0.118724</v>
       </c>
       <c r="E106" s="9" t="n"/>
     </row>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>38053.31</v>
+        <v>94956.27</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.004506</v>
+        <v>0.009308</v>
       </c>
       <c r="E107" s="9" t="n"/>
     </row>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="C108" s="8" t="n">
-        <v>38053.31</v>
+        <v>93468.78</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.004506</v>
+        <v>0.009162999999999999</v>
       </c>
       <c r="E108" s="9" t="n"/>
     </row>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>0</v>
+        <v>1487.49</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0</v>
+        <v>0.000146</v>
       </c>
       <c r="E109" s="9" t="n"/>
     </row>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="C110" s="8" t="n">
-        <v>0</v>
+        <v>11778.1</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0</v>
+        <v>0.001155</v>
       </c>
       <c r="E110" s="9" t="n"/>
     </row>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>0</v>
+        <v>2403.8</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0</v>
+        <v>0.000236</v>
       </c>
       <c r="E111" s="9" t="n"/>
     </row>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="C112" s="8" t="n">
-        <v>0</v>
+        <v>685.46</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0</v>
+        <v>6.7e-05</v>
       </c>
       <c r="E112" s="9" t="n"/>
     </row>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>0</v>
+        <v>4321.03</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0</v>
+        <v>0.000424</v>
       </c>
       <c r="E113" s="9" t="n"/>
     </row>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="C114" s="8" t="n">
-        <v>0</v>
+        <v>662.13</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0</v>
+        <v>6.499999999999999e-05</v>
       </c>
       <c r="E114" s="9" t="n"/>
     </row>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>0</v>
+        <v>2906.92</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0</v>
+        <v>0.000285</v>
       </c>
       <c r="E115" s="9" t="n"/>
     </row>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>0</v>
+        <v>798.77</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0</v>
+        <v>7.8e-05</v>
       </c>
       <c r="E117" s="9" t="n"/>
     </row>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>2143315.5</v>
+        <v>2468356.87</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.253778</v>
+        <v>0.241968</v>
       </c>
       <c r="E119" s="9" t="n"/>
     </row>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="C120" s="8" t="n">
-        <v>0</v>
+        <v>30419.2</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0</v>
+        <v>0.002982</v>
       </c>
       <c r="E120" s="9" t="n"/>
     </row>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>94937.73</v>
+        <v>95789.84</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.011241</v>
+        <v>0.009389999999999999</v>
       </c>
       <c r="E121" s="9" t="n"/>
     </row>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="C122" s="8" t="n">
-        <v>0</v>
+        <v>500.6</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0</v>
+        <v>4.9e-05</v>
       </c>
       <c r="E122" s="9" t="n"/>
     </row>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>0</v>
+        <v>2404.85</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0</v>
+        <v>0.000236</v>
       </c>
       <c r="E123" s="9" t="n"/>
     </row>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>0</v>
+        <v>6092.47</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0</v>
+        <v>0.000597</v>
       </c>
       <c r="E125" s="9" t="n"/>
     </row>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="C126" s="8" t="n">
-        <v>0</v>
+        <v>233161.28</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0</v>
+        <v>0.022856</v>
       </c>
       <c r="E126" s="9" t="n"/>
     </row>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>0</v>
+        <v>85400.49000000001</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0</v>
+        <v>0.008372000000000001</v>
       </c>
       <c r="E127" s="9" t="n"/>
     </row>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="C128" s="8" t="n">
-        <v>0</v>
+        <v>1703.7</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0</v>
+        <v>0.000167</v>
       </c>
       <c r="E128" s="9" t="n"/>
     </row>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>0</v>
+        <v>1258.64</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0</v>
+        <v>0.000123</v>
       </c>
       <c r="E129" s="9" t="n"/>
     </row>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="C130" s="8" t="n">
-        <v>2048377.76</v>
+        <v>2000816.48</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.242537</v>
+        <v>0.196136</v>
       </c>
       <c r="E130" s="9" t="n"/>
     </row>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>0</v>
+        <v>8681.67</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0</v>
+        <v>0.000851</v>
       </c>
       <c r="E131" s="9" t="n"/>
     </row>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="C132" s="8" t="n">
-        <v>0</v>
+        <v>1601.39</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0</v>
+        <v>0.000157</v>
       </c>
       <c r="E132" s="9" t="n"/>
     </row>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>0</v>
+        <v>526.26</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0</v>
+        <v>5.2e-05</v>
       </c>
       <c r="E133" s="9" t="n"/>
     </row>
@@ -3001,13 +3001,13 @@
         </is>
       </c>
       <c r="C134" s="5" t="n">
-        <v>0</v>
+        <v>46844.53</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>0</v>
+        <v>0.000307</v>
       </c>
     </row>
     <row r="135">
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1508929.53</v>
+        <v>1511182.22</v>
       </c>
       <c r="D135" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>0.009889999999999999</v>
+        <v>0.009905000000000001</v>
       </c>
     </row>
     <row r="136">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>1508929.53</v>
+        <v>1510114.48</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1</v>
+        <v>0.999293</v>
       </c>
       <c r="E137" s="9" t="n"/>
     </row>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="C138" s="8" t="n">
-        <v>0</v>
+        <v>1067.74</v>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0</v>
+        <v>0.0007069999999999999</v>
       </c>
       <c r="E138" s="9" t="n"/>
     </row>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="C140" s="5" t="n">
-        <v>1553182.89</v>
+        <v>1867566.23</v>
       </c>
       <c r="D140" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>0.010181</v>
+        <v>0.012241</v>
       </c>
     </row>
     <row r="141">

--- a/data/informes/cuadro_10_4.xlsx
+++ b/data/informes/cuadro_10_4.xlsx
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>44116686.04</v>
+        <v>44866893.14</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.289168</v>
+        <v>0.293982</v>
       </c>
     </row>
     <row r="5">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>43344452.16</v>
+        <v>44101559.05</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.982496</v>
+        <v>0.982942</v>
       </c>
       <c r="E5" s="9" t="n"/>
     </row>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>13448114.45</v>
+        <v>13654504.36</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.304831</v>
+        <v>0.304334</v>
       </c>
       <c r="E6" s="9" t="n"/>
     </row>
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>12192854.28</v>
+        <v>12381663.41</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.276377</v>
+        <v>0.275964</v>
       </c>
       <c r="E7" s="9" t="n"/>
     </row>
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>9926251.35</v>
+        <v>10083290.38</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.225</v>
+        <v>0.224738</v>
       </c>
       <c r="E8" s="9" t="n"/>
     </row>
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>7747720.95</v>
+        <v>7952854.05</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.175619</v>
+        <v>0.177254</v>
       </c>
       <c r="E9" s="9" t="n"/>
     </row>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>763971.37</v>
+        <v>757145.5699999999</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.017317</v>
+        <v>0.016875</v>
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>763971.37</v>
+        <v>757145.5699999999</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.017317</v>
+        <v>0.016875</v>
       </c>
       <c r="E12" s="9" t="n"/>
     </row>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>65298325.24</v>
+        <v>64780387.29</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.4280060000000001</v>
+        <v>0.424461</v>
       </c>
     </row>
     <row r="14">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>64081763.57</v>
+        <v>63574020.03</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.9813689999999999</v>
+        <v>0.981378</v>
       </c>
       <c r="E14" s="9" t="n"/>
     </row>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>673601.35</v>
+        <v>668899.71</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.010316</v>
+        <v>0.010326</v>
       </c>
       <c r="E15" s="9" t="n"/>
     </row>
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>775238.16</v>
+        <v>769020.05</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.011872</v>
+        <v>0.011871</v>
       </c>
       <c r="E16" s="9" t="n"/>
     </row>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1451832.52</v>
+        <v>1440684.15</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.022234</v>
+        <v>0.02224</v>
       </c>
       <c r="E17" s="9" t="n"/>
     </row>
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>273494.98</v>
+        <v>271680.17</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.004188</v>
+        <v>0.004194</v>
       </c>
       <c r="E18" s="9" t="n"/>
     </row>
@@ -811,7 +811,7 @@
         <v>69722.33</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.001068</v>
+        <v>0.001076</v>
       </c>
       <c r="E19" s="9" t="n"/>
     </row>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>45966.01</v>
+        <v>45815.95</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.0007040000000000001</v>
+        <v>0.0007069999999999999</v>
       </c>
       <c r="E20" s="9" t="n"/>
     </row>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>281652.05</v>
+        <v>279886.24</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.004313</v>
+        <v>0.004321</v>
       </c>
       <c r="E21" s="9" t="n"/>
     </row>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>495607.62</v>
+        <v>491717.15</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.00759</v>
+        <v>0.007591</v>
       </c>
       <c r="E22" s="9" t="n"/>
     </row>
@@ -884,10 +884,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>157919.23</v>
+        <v>157304.89</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.002418</v>
+        <v>0.002428</v>
       </c>
       <c r="E23" s="9" t="n"/>
     </row>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>1888008.69</v>
+        <v>1873302.49</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.028914</v>
+        <v>0.028918</v>
       </c>
       <c r="E24" s="9" t="n"/>
     </row>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>6961520.04</v>
+        <v>6905897.94</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.106611</v>
+        <v>0.106605</v>
       </c>
       <c r="E25" s="9" t="n"/>
     </row>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>5372339.32</v>
+        <v>5328351.55</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.082274</v>
+        <v>0.08225300000000001</v>
       </c>
       <c r="E26" s="9" t="n"/>
     </row>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>2210114.43</v>
+        <v>2194717.99</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.033846</v>
+        <v>0.033879</v>
       </c>
       <c r="E27" s="9" t="n"/>
     </row>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>1940901.07</v>
+        <v>1926943.19</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.029724</v>
+        <v>0.029746</v>
       </c>
       <c r="E28" s="9" t="n"/>
     </row>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>258834.04</v>
+        <v>256966.66</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.003964</v>
+        <v>0.003967</v>
       </c>
       <c r="E29" s="9" t="n"/>
     </row>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>156078.82</v>
+        <v>154847.25</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>0.00239</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>41068932.91</v>
+        <v>40738262.32</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.628943</v>
+        <v>0.628867</v>
       </c>
       <c r="E31" s="9" t="n"/>
     </row>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>1005577.74</v>
+        <v>997165.48</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.0154</v>
+        <v>0.015393</v>
       </c>
       <c r="E34" s="9" t="n"/>
     </row>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>210983.93</v>
+        <v>209201.78</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.003231</v>
+        <v>0.003229</v>
       </c>
       <c r="E35" s="9" t="n"/>
     </row>
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>22346700.44</v>
+        <v>22210152.32</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.146474</v>
+        <v>0.145528</v>
       </c>
     </row>
     <row r="37">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>15538027.33</v>
+        <v>15457417.76</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.6953159999999999</v>
+        <v>0.695962</v>
       </c>
       <c r="E37" s="9" t="n"/>
     </row>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>457438.3</v>
+        <v>454756.05</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.02047</v>
+        <v>0.020475</v>
       </c>
       <c r="E38" s="9" t="n"/>
     </row>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>1064763.24</v>
+        <v>1059363.7</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.047647</v>
+        <v>0.047697</v>
       </c>
       <c r="E39" s="9" t="n"/>
     </row>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>316293.39</v>
+        <v>315012.57</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.014154</v>
+        <v>0.014183</v>
       </c>
       <c r="E40" s="9" t="n"/>
     </row>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>110774.26</v>
+        <v>110401.34</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.004957</v>
+        <v>0.004971</v>
       </c>
       <c r="E41" s="9" t="n"/>
     </row>
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>304047.3</v>
+        <v>302367.15</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.013606</v>
+        <v>0.013614</v>
       </c>
       <c r="E42" s="9" t="n"/>
     </row>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>673147.0699999999</v>
+        <v>668345.59</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.030123</v>
+        <v>0.030092</v>
       </c>
       <c r="E43" s="9" t="n"/>
     </row>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>161242.21</v>
+        <v>160224.39</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.007215</v>
+        <v>0.007214000000000001</v>
       </c>
       <c r="E44" s="9" t="n"/>
     </row>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>437068.08</v>
+        <v>435915.38</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.019559</v>
+        <v>0.019627</v>
       </c>
       <c r="E45" s="9" t="n"/>
     </row>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>209289.82</v>
+        <v>208169.1</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.009365999999999999</v>
+        <v>0.009372999999999999</v>
       </c>
       <c r="E46" s="9" t="n"/>
     </row>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>156344.94</v>
+        <v>155490.03</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.006996</v>
+        <v>0.007000999999999999</v>
       </c>
       <c r="E47" s="9" t="n"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>306867.68</v>
+        <v>304981.29</v>
       </c>
       <c r="D48" s="9" t="n">
         <v>0.013732</v>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>586672.96</v>
+        <v>583848.47</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.026253</v>
+        <v>0.026287</v>
       </c>
       <c r="E49" s="9" t="n"/>
     </row>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>364871.41</v>
+        <v>362639.86</v>
       </c>
       <c r="D50" s="9" t="n">
         <v>0.016328</v>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>1782106.91</v>
+        <v>1771510.17</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.079748</v>
+        <v>0.079761</v>
       </c>
       <c r="E51" s="9" t="n"/>
     </row>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>1182295.25</v>
+        <v>1177923.15</v>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.052907</v>
+        <v>0.053035</v>
       </c>
       <c r="E52" s="9" t="n"/>
     </row>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>528667.15</v>
+        <v>525313.22</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.023658</v>
+        <v>0.023652</v>
       </c>
       <c r="E53" s="9" t="n"/>
     </row>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>1470919.81</v>
+        <v>1462788.1</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.06582300000000001</v>
+        <v>0.065861</v>
       </c>
       <c r="E54" s="9" t="n"/>
     </row>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>414126.09</v>
+        <v>413757.71</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.018532</v>
+        <v>0.018629</v>
       </c>
       <c r="E55" s="9" t="n"/>
     </row>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>435500.93</v>
+        <v>433995.14</v>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.019488</v>
+        <v>0.01954</v>
       </c>
       <c r="E56" s="9" t="n"/>
     </row>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>276477.89</v>
+        <v>275031.13</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.012372</v>
+        <v>0.012383</v>
       </c>
       <c r="E57" s="9" t="n"/>
     </row>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>1383529.14</v>
+        <v>1373759.08</v>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.061912</v>
+        <v>0.061853</v>
       </c>
       <c r="E58" s="9" t="n"/>
     </row>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>384103.02</v>
+        <v>382415.66</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.017188</v>
+        <v>0.017218</v>
       </c>
       <c r="E59" s="9" t="n"/>
     </row>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="C60" s="8" t="n">
-        <v>516302.8</v>
+        <v>514364.34</v>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.023104</v>
+        <v>0.023159</v>
       </c>
       <c r="E60" s="9" t="n"/>
     </row>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>816602.62</v>
+        <v>812588.5</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.036542</v>
+        <v>0.036586</v>
       </c>
       <c r="E61" s="9" t="n"/>
     </row>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>308711.13</v>
+        <v>307293.22</v>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.013815</v>
+        <v>0.013836</v>
       </c>
       <c r="E62" s="9" t="n"/>
     </row>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>96448.96000000001</v>
+        <v>96242.81</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.004316</v>
+        <v>0.004333</v>
       </c>
       <c r="E63" s="9" t="n"/>
     </row>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="C64" s="8" t="n">
-        <v>200961.32</v>
+        <v>199900.47</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.008992999999999999</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="E64" s="9" t="n"/>
     </row>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>592453.64</v>
+        <v>589020.16</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.026512</v>
+        <v>0.02652</v>
       </c>
       <c r="E65" s="9" t="n"/>
     </row>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="C66" s="8" t="n">
-        <v>6808673.12</v>
+        <v>6752734.56</v>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.304684</v>
+        <v>0.304038</v>
       </c>
       <c r="E66" s="9" t="n"/>
     </row>
@@ -1760,13 +1760,13 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>2603348.33</v>
+        <v>2594852.65</v>
       </c>
       <c r="D69" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>0.017064</v>
+        <v>0.017002</v>
       </c>
     </row>
     <row r="70">
@@ -1784,7 +1784,7 @@
         <v>39322.9</v>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.015105</v>
+        <v>0.015154</v>
       </c>
       <c r="E70" s="9" t="n"/>
     </row>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>717102.83</v>
+        <v>710793.55</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.275454</v>
+        <v>0.273924</v>
       </c>
       <c r="E71" s="9" t="n"/>
     </row>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="C72" s="8" t="n">
-        <v>7940.29</v>
+        <v>7932.1</v>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.00305</v>
+        <v>0.003057</v>
       </c>
       <c r="E72" s="9" t="n"/>
     </row>
@@ -1841,7 +1841,7 @@
         <v>723.67</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.000278</v>
+        <v>0.000279</v>
       </c>
       <c r="E73" s="9" t="n"/>
     </row>
@@ -1860,7 +1860,7 @@
         <v>3560.1</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.001368</v>
+        <v>0.001372</v>
       </c>
       <c r="E74" s="9" t="n"/>
     </row>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>361721.48</v>
+        <v>358491.83</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.138945</v>
+        <v>0.138155</v>
       </c>
       <c r="E75" s="9" t="n"/>
     </row>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="C76" s="8" t="n">
-        <v>329957.69</v>
+        <v>326994.77</v>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.126744</v>
+        <v>0.126017</v>
       </c>
       <c r="E76" s="9" t="n"/>
     </row>
@@ -1917,7 +1917,7 @@
         <v>753.9299999999999</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.00029</v>
+        <v>0.000291</v>
       </c>
       <c r="E77" s="9" t="n"/>
     </row>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="C78" s="8" t="n">
-        <v>12445.67</v>
+        <v>12337.15</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.004781000000000001</v>
+        <v>0.004754</v>
       </c>
       <c r="E78" s="9" t="n"/>
     </row>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>1734239.61</v>
+        <v>1732181.06</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.666157</v>
+        <v>0.6675449999999999</v>
       </c>
       <c r="E79" s="9" t="n"/>
     </row>
@@ -1974,7 +1974,7 @@
         <v>9365.389999999999</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.003597</v>
+        <v>0.003609</v>
       </c>
       <c r="E80" s="9" t="n"/>
     </row>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>1429207.85</v>
+        <v>1427862.29</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.548988</v>
+        <v>0.550267</v>
       </c>
       <c r="E81" s="9" t="n"/>
     </row>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>295666.37</v>
+        <v>294953.37</v>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.113572</v>
+        <v>0.113669</v>
       </c>
       <c r="E82" s="9" t="n"/>
     </row>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>112682.99</v>
+        <v>112555.14</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.043284</v>
+        <v>0.043376</v>
       </c>
       <c r="E83" s="9" t="n"/>
     </row>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="C86" s="8" t="n">
-        <v>60456.79</v>
+        <v>60328.94</v>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.023223</v>
+        <v>0.023249</v>
       </c>
       <c r="E86" s="9" t="n"/>
     </row>
@@ -2107,7 +2107,7 @@
         <v>51418.56</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.019751</v>
+        <v>0.019816</v>
       </c>
       <c r="E87" s="9" t="n"/>
     </row>
@@ -2126,7 +2126,7 @@
         <v>807.64</v>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.00031</v>
+        <v>0.000311</v>
       </c>
       <c r="E88" s="9" t="n"/>
     </row>
@@ -2142,13 +2142,13 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>4572140.75</v>
+        <v>4558898.88</v>
       </c>
       <c r="D89" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>0.029969</v>
+        <v>0.029871</v>
       </c>
     </row>
     <row r="90">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="C90" s="8" t="n">
-        <v>1414702.44</v>
+        <v>1406304.63</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.309418</v>
+        <v>0.308475</v>
       </c>
       <c r="E90" s="9" t="n"/>
     </row>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>2390006.49</v>
+        <v>2387165.87</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.522732</v>
+        <v>0.523628</v>
       </c>
       <c r="E91" s="9" t="n"/>
     </row>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>605336.4</v>
+        <v>604396.12</v>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.132397</v>
+        <v>0.132575</v>
       </c>
       <c r="E92" s="9" t="n"/>
     </row>
@@ -2242,7 +2242,7 @@
         <v>45523.14</v>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.009957000000000001</v>
+        <v>0.009986</v>
       </c>
       <c r="E94" s="9" t="n"/>
     </row>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>10201156.61</v>
+        <v>10127335.46</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>0.06686499999999999</v>
+        <v>0.066357</v>
       </c>
     </row>
     <row r="96">
@@ -2282,7 +2282,7 @@
         <v>73023.05</v>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.007158</v>
+        <v>0.007209999999999999</v>
       </c>
       <c r="E96" s="9" t="n"/>
     </row>
@@ -2301,7 +2301,7 @@
         <v>72220.78999999999</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.007079999999999999</v>
+        <v>0.007130999999999999</v>
       </c>
       <c r="E97" s="9" t="n"/>
     </row>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>6336981.46</v>
+        <v>6285000.41</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.6212019999999999</v>
+        <v>0.620598</v>
       </c>
       <c r="E101" s="9" t="n"/>
     </row>
@@ -2396,7 +2396,7 @@
         <v>4936.7</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.000484</v>
+        <v>0.000487</v>
       </c>
       <c r="E102" s="9" t="n"/>
     </row>
@@ -2415,7 +2415,7 @@
         <v>3129.05</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.000307</v>
+        <v>0.000309</v>
       </c>
       <c r="E103" s="9" t="n"/>
     </row>
@@ -2434,7 +2434,7 @@
         <v>1038.52</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.000102</v>
+        <v>0.000103</v>
       </c>
       <c r="E104" s="9" t="n"/>
     </row>
@@ -2453,7 +2453,7 @@
         <v>769.12</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>7.499999999999999e-05</v>
+        <v>7.6e-05</v>
       </c>
       <c r="E105" s="9" t="n"/>
     </row>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="C106" s="8" t="n">
-        <v>1211124.17</v>
+        <v>1208424.36</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.118724</v>
+        <v>0.119323</v>
       </c>
       <c r="E106" s="9" t="n"/>
     </row>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>94956.27</v>
+        <v>94622.37</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.009308</v>
+        <v>0.009343000000000001</v>
       </c>
       <c r="E107" s="9" t="n"/>
     </row>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="C108" s="8" t="n">
-        <v>93468.78</v>
+        <v>93134.89</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.009162999999999999</v>
+        <v>0.009195999999999999</v>
       </c>
       <c r="E108" s="9" t="n"/>
     </row>
@@ -2529,7 +2529,7 @@
         <v>1487.49</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.000146</v>
+        <v>0.000147</v>
       </c>
       <c r="E109" s="9" t="n"/>
     </row>
@@ -2548,7 +2548,7 @@
         <v>11778.1</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.001155</v>
+        <v>0.001163</v>
       </c>
       <c r="E110" s="9" t="n"/>
     </row>
@@ -2567,7 +2567,7 @@
         <v>2403.8</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.000236</v>
+        <v>0.000237</v>
       </c>
       <c r="E111" s="9" t="n"/>
     </row>
@@ -2586,7 +2586,7 @@
         <v>685.46</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>6.7e-05</v>
+        <v>6.8e-05</v>
       </c>
       <c r="E112" s="9" t="n"/>
     </row>
@@ -2605,7 +2605,7 @@
         <v>4321.03</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.000424</v>
+        <v>0.000427</v>
       </c>
       <c r="E113" s="9" t="n"/>
     </row>
@@ -2643,7 +2643,7 @@
         <v>2906.92</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.000285</v>
+        <v>0.000287</v>
       </c>
       <c r="E115" s="9" t="n"/>
     </row>
@@ -2681,7 +2681,7 @@
         <v>798.77</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>7.8e-05</v>
+        <v>7.900000000000001e-05</v>
       </c>
       <c r="E117" s="9" t="n"/>
     </row>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>2468356.87</v>
+        <v>2449550.47</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.241968</v>
+        <v>0.241875</v>
       </c>
       <c r="E119" s="9" t="n"/>
     </row>
@@ -2738,7 +2738,7 @@
         <v>30419.2</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.002982</v>
+        <v>0.003004</v>
       </c>
       <c r="E120" s="9" t="n"/>
     </row>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>95789.84</v>
+        <v>94956.81</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.009389999999999999</v>
+        <v>0.009376000000000001</v>
       </c>
       <c r="E121" s="9" t="n"/>
     </row>
@@ -2795,7 +2795,7 @@
         <v>2404.85</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.000236</v>
+        <v>0.000237</v>
       </c>
       <c r="E123" s="9" t="n"/>
     </row>
@@ -2833,7 +2833,7 @@
         <v>6092.47</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.000597</v>
+        <v>0.000602</v>
       </c>
       <c r="E125" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         <v>233161.28</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.022856</v>
+        <v>0.023023</v>
       </c>
       <c r="E126" s="9" t="n"/>
     </row>
@@ -2871,7 +2871,7 @@
         <v>85400.49000000001</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.008372000000000001</v>
+        <v>0.008433000000000001</v>
       </c>
       <c r="E127" s="9" t="n"/>
     </row>
@@ -2890,7 +2890,7 @@
         <v>1703.7</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.000167</v>
+        <v>0.000168</v>
       </c>
       <c r="E128" s="9" t="n"/>
     </row>
@@ -2909,7 +2909,7 @@
         <v>1258.64</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.000123</v>
+        <v>0.000124</v>
       </c>
       <c r="E129" s="9" t="n"/>
     </row>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="C130" s="8" t="n">
-        <v>2000816.48</v>
+        <v>1982843.11</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.196136</v>
+        <v>0.195791</v>
       </c>
       <c r="E130" s="9" t="n"/>
     </row>
@@ -2947,7 +2947,7 @@
         <v>8681.67</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.000851</v>
+        <v>0.000857</v>
       </c>
       <c r="E131" s="9" t="n"/>
     </row>
@@ -2966,7 +2966,7 @@
         <v>1601.39</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.000157</v>
+        <v>0.000158</v>
       </c>
       <c r="E132" s="9" t="n"/>
     </row>
@@ -3028,7 +3028,7 @@
         <v>1</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>0.009905000000000001</v>
+        <v>0.009901999999999999</v>
       </c>
     </row>
     <row r="136">
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="C140" s="5" t="n">
-        <v>1867566.23</v>
+        <v>1921346.53</v>
       </c>
       <c r="D140" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>0.012241</v>
+        <v>0.012589</v>
       </c>
     </row>
     <row r="141">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>152563950.4</v>
+        <v>152617893.03</v>
       </c>
       <c r="D141" s="10" t="n"/>
       <c r="E141" s="12" t="n">

--- a/data/informes/cuadro_10_4.xlsx
+++ b/data/informes/cuadro_10_4.xlsx
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>44866893.14</v>
+        <v>45500596.73</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.293982</v>
+        <v>0.298134</v>
       </c>
     </row>
     <row r="5">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>44101559.05</v>
+        <v>44720946.75</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.982942</v>
+        <v>0.982865</v>
       </c>
       <c r="E5" s="9" t="n"/>
     </row>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>13654504.36</v>
+        <v>13842944.36</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.304334</v>
+        <v>0.304237</v>
       </c>
       <c r="E6" s="9" t="n"/>
     </row>
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>12381663.41</v>
+        <v>12559538.77</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.275964</v>
+        <v>0.27603</v>
       </c>
       <c r="E7" s="9" t="n"/>
     </row>
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>10083290.38</v>
+        <v>10228976.62</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.224738</v>
+        <v>0.22481</v>
       </c>
       <c r="E8" s="9" t="n"/>
     </row>
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>7952854.05</v>
+        <v>8059694.2</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.177254</v>
+        <v>0.177134</v>
       </c>
       <c r="E9" s="9" t="n"/>
     </row>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>757145.5699999999</v>
+        <v>771308.6</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.016875</v>
+        <v>0.016952</v>
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>757145.5699999999</v>
+        <v>771308.6</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.016875</v>
+        <v>0.016952</v>
       </c>
       <c r="E12" s="9" t="n"/>
     </row>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>64780387.29</v>
+        <v>66948393.92</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.424461</v>
+        <v>0.438667</v>
       </c>
     </row>
     <row r="14">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>63574020.03</v>
+        <v>65720967.27</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.981378</v>
+        <v>0.981666</v>
       </c>
       <c r="E14" s="9" t="n"/>
     </row>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>668899.71</v>
+        <v>678612.26</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.010326</v>
+        <v>0.010136</v>
       </c>
       <c r="E15" s="9" t="n"/>
     </row>
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>769020.05</v>
+        <v>786060.63</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.011871</v>
+        <v>0.011741</v>
       </c>
       <c r="E16" s="9" t="n"/>
     </row>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1440684.15</v>
+        <v>1463772.43</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.02224</v>
+        <v>0.021864</v>
       </c>
       <c r="E17" s="9" t="n"/>
     </row>
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>271680.17</v>
+        <v>275429.17</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.004194</v>
+        <v>0.004114</v>
       </c>
       <c r="E18" s="9" t="n"/>
     </row>
@@ -811,7 +811,7 @@
         <v>69722.33</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.001076</v>
+        <v>0.001041</v>
       </c>
       <c r="E19" s="9" t="n"/>
     </row>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>45815.95</v>
+        <v>46125.94</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.0007069999999999999</v>
+        <v>0.0006890000000000001</v>
       </c>
       <c r="E20" s="9" t="n"/>
     </row>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>279886.24</v>
+        <v>283534.02</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.004321</v>
+        <v>0.004235</v>
       </c>
       <c r="E21" s="9" t="n"/>
     </row>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>491717.15</v>
+        <v>507708.96</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.007591</v>
+        <v>0.007584</v>
       </c>
       <c r="E22" s="9" t="n"/>
     </row>
@@ -884,10 +884,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>157304.89</v>
+        <v>158573.98</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.002428</v>
+        <v>0.002369</v>
       </c>
       <c r="E23" s="9" t="n"/>
     </row>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>1873302.49</v>
+        <v>1903682.25</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.028918</v>
+        <v>0.028435</v>
       </c>
       <c r="E24" s="9" t="n"/>
     </row>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>6905897.94</v>
+        <v>7613288.87</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.106605</v>
+        <v>0.113719</v>
       </c>
       <c r="E25" s="9" t="n"/>
     </row>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>5328351.55</v>
+        <v>5436322.41</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.08225300000000001</v>
+        <v>0.08120200000000001</v>
       </c>
       <c r="E26" s="9" t="n"/>
     </row>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>2194717.99</v>
+        <v>2384329.59</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.033879</v>
+        <v>0.035614</v>
       </c>
       <c r="E27" s="9" t="n"/>
     </row>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>1926943.19</v>
+        <v>2101249.84</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.029746</v>
+        <v>0.031386</v>
       </c>
       <c r="E28" s="9" t="n"/>
     </row>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>256966.66</v>
+        <v>260824.26</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.003967</v>
+        <v>0.003896</v>
       </c>
       <c r="E29" s="9" t="n"/>
     </row>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>154847.25</v>
+        <v>157391.4</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.00239</v>
+        <v>0.002351</v>
       </c>
       <c r="E30" s="9" t="n"/>
     </row>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>40738262.32</v>
+        <v>41594338.92</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.628867</v>
+        <v>0.62129</v>
       </c>
       <c r="E31" s="9" t="n"/>
     </row>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>997165.48</v>
+        <v>1014543.36</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.015393</v>
+        <v>0.015154</v>
       </c>
       <c r="E34" s="9" t="n"/>
     </row>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>209201.78</v>
+        <v>212883.3</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.003229</v>
+        <v>0.00318</v>
       </c>
       <c r="E35" s="9" t="n"/>
     </row>
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>22210152.32</v>
+        <v>22887797.62</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.145528</v>
+        <v>0.149968</v>
       </c>
     </row>
     <row r="37">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>15457417.76</v>
+        <v>16021056.82</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.695962</v>
+        <v>0.699982</v>
       </c>
       <c r="E37" s="9" t="n"/>
     </row>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>454756.05</v>
+        <v>472236.3</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.020475</v>
+        <v>0.020633</v>
       </c>
       <c r="E38" s="9" t="n"/>
     </row>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>1059363.7</v>
+        <v>1072904.43</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.047697</v>
+        <v>0.046877</v>
       </c>
       <c r="E39" s="9" t="n"/>
     </row>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>315012.57</v>
+        <v>318011.99</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.014183</v>
+        <v>0.013894</v>
       </c>
       <c r="E40" s="9" t="n"/>
     </row>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>110401.34</v>
+        <v>111171.72</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.004971</v>
+        <v>0.004857</v>
       </c>
       <c r="E41" s="9" t="n"/>
     </row>
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>302367.15</v>
+        <v>306435.24</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.013614</v>
+        <v>0.013389</v>
       </c>
       <c r="E42" s="9" t="n"/>
     </row>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>668345.59</v>
+        <v>700207.8100000001</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.030092</v>
+        <v>0.030593</v>
       </c>
       <c r="E43" s="9" t="n"/>
     </row>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>160224.39</v>
+        <v>165779.85</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.007214000000000001</v>
+        <v>0.007243</v>
       </c>
       <c r="E44" s="9" t="n"/>
     </row>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>435915.38</v>
+        <v>448641.74</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.019627</v>
+        <v>0.019602</v>
       </c>
       <c r="E45" s="9" t="n"/>
     </row>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>208169.1</v>
+        <v>212081.9</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.009372999999999999</v>
+        <v>0.009266</v>
       </c>
       <c r="E46" s="9" t="n"/>
     </row>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>155490.03</v>
+        <v>157256.08</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.007000999999999999</v>
+        <v>0.006871</v>
       </c>
       <c r="E47" s="9" t="n"/>
     </row>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>304981.29</v>
+        <v>325853.52</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.013732</v>
+        <v>0.014237</v>
       </c>
       <c r="E48" s="9" t="n"/>
     </row>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>583848.47</v>
+        <v>591152.49</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.026287</v>
+        <v>0.025828</v>
       </c>
       <c r="E49" s="9" t="n"/>
     </row>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>362639.86</v>
+        <v>384507</v>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.016328</v>
+        <v>0.0168</v>
       </c>
       <c r="E50" s="9" t="n"/>
     </row>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>1771510.17</v>
+        <v>1920146.15</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.079761</v>
+        <v>0.083894</v>
       </c>
       <c r="E51" s="9" t="n"/>
     </row>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>1177923.15</v>
+        <v>1187662.32</v>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.053035</v>
+        <v>0.051891</v>
       </c>
       <c r="E52" s="9" t="n"/>
     </row>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>525313.22</v>
+        <v>599558.54</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.023652</v>
+        <v>0.026196</v>
       </c>
       <c r="E53" s="9" t="n"/>
     </row>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>1462788.1</v>
+        <v>1479894.73</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.065861</v>
+        <v>0.06465900000000001</v>
       </c>
       <c r="E54" s="9" t="n"/>
     </row>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>413757.71</v>
+        <v>414550.55</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.018629</v>
+        <v>0.018112</v>
       </c>
       <c r="E55" s="9" t="n"/>
     </row>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>433995.14</v>
+        <v>437105.78</v>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.01954</v>
+        <v>0.019098</v>
       </c>
       <c r="E56" s="9" t="n"/>
     </row>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>275031.13</v>
+        <v>280072.79</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.012383</v>
+        <v>0.012237</v>
       </c>
       <c r="E57" s="9" t="n"/>
     </row>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>1373759.08</v>
+        <v>1394594.66</v>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.061853</v>
+        <v>0.06093200000000001</v>
       </c>
       <c r="E58" s="9" t="n"/>
     </row>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>382415.66</v>
+        <v>435974.94</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.017218</v>
+        <v>0.019048</v>
       </c>
       <c r="E59" s="9" t="n"/>
     </row>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="C60" s="8" t="n">
-        <v>514364.34</v>
+        <v>522289.46</v>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.023159</v>
+        <v>0.02282</v>
       </c>
       <c r="E60" s="9" t="n"/>
     </row>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>812588.5</v>
+        <v>820880.8</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.036586</v>
+        <v>0.035865</v>
       </c>
       <c r="E61" s="9" t="n"/>
     </row>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>307293.22</v>
+        <v>310222.31</v>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.013836</v>
+        <v>0.013554</v>
       </c>
       <c r="E62" s="9" t="n"/>
     </row>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>96242.81</v>
+        <v>96668.66</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.004333</v>
+        <v>0.004224</v>
       </c>
       <c r="E63" s="9" t="n"/>
     </row>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="C64" s="8" t="n">
-        <v>199900.47</v>
+        <v>216989.22</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.009481</v>
       </c>
       <c r="E64" s="9" t="n"/>
     </row>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>589020.16</v>
+        <v>638205.83</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.02652</v>
+        <v>0.027884</v>
       </c>
       <c r="E65" s="9" t="n"/>
     </row>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="C66" s="8" t="n">
-        <v>6752734.56</v>
+        <v>6866740.8</v>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.304038</v>
+        <v>0.300018</v>
       </c>
       <c r="E66" s="9" t="n"/>
     </row>
@@ -1760,13 +1760,13 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>2594852.65</v>
+        <v>969690.79</v>
       </c>
       <c r="D69" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>0.017002</v>
+        <v>0.006353999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="C70" s="8" t="n">
-        <v>39322.9</v>
+        <v>0</v>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.015154</v>
+        <v>0</v>
       </c>
       <c r="E70" s="9" t="n"/>
     </row>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>710793.55</v>
+        <v>709377.4399999999</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.273924</v>
+        <v>0.73155</v>
       </c>
       <c r="E71" s="9" t="n"/>
     </row>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="C72" s="8" t="n">
-        <v>7932.1</v>
+        <v>977.92</v>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.003057</v>
+        <v>0.001008</v>
       </c>
       <c r="E72" s="9" t="n"/>
     </row>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>723.67</v>
+        <v>0</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.000279</v>
+        <v>0</v>
       </c>
       <c r="E73" s="9" t="n"/>
     </row>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="C74" s="8" t="n">
-        <v>3560.1</v>
+        <v>0</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.001372</v>
+        <v>0</v>
       </c>
       <c r="E74" s="9" t="n"/>
     </row>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>358491.83</v>
+        <v>364059.11</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.138155</v>
+        <v>0.375438</v>
       </c>
       <c r="E75" s="9" t="n"/>
     </row>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="C76" s="8" t="n">
-        <v>326994.77</v>
+        <v>332174.59</v>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.126017</v>
+        <v>0.342557</v>
       </c>
       <c r="E76" s="9" t="n"/>
     </row>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>753.9299999999999</v>
+        <v>0</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.000291</v>
+        <v>0</v>
       </c>
       <c r="E77" s="9" t="n"/>
     </row>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="C78" s="8" t="n">
-        <v>12337.15</v>
+        <v>12165.81</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.004754</v>
+        <v>0.012546</v>
       </c>
       <c r="E78" s="9" t="n"/>
     </row>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>1732181.06</v>
+        <v>245901.11</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.6675449999999999</v>
+        <v>0.253587</v>
       </c>
       <c r="E79" s="9" t="n"/>
     </row>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="C80" s="8" t="n">
-        <v>9365.389999999999</v>
+        <v>0</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.003609</v>
+        <v>0</v>
       </c>
       <c r="E80" s="9" t="n"/>
     </row>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>1427862.29</v>
+        <v>160731.1</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.550267</v>
+        <v>0.165755</v>
       </c>
       <c r="E81" s="9" t="n"/>
     </row>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>294953.37</v>
+        <v>85170.00999999999</v>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.113669</v>
+        <v>0.08783200000000001</v>
       </c>
       <c r="E82" s="9" t="n"/>
     </row>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>112555.14</v>
+        <v>14412.24</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.043376</v>
+        <v>0.014863</v>
       </c>
       <c r="E83" s="9" t="n"/>
     </row>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="C86" s="8" t="n">
-        <v>60328.94</v>
+        <v>14412.24</v>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.023249</v>
+        <v>0.014863</v>
       </c>
       <c r="E86" s="9" t="n"/>
     </row>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>51418.56</v>
+        <v>0</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.019816</v>
+        <v>0</v>
       </c>
       <c r="E87" s="9" t="n"/>
     </row>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="C88" s="8" t="n">
-        <v>807.64</v>
+        <v>0</v>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.000311</v>
+        <v>0</v>
       </c>
       <c r="E88" s="9" t="n"/>
     </row>
@@ -2142,13 +2142,13 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>4558898.88</v>
+        <v>4557206.92</v>
       </c>
       <c r="D89" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>0.029871</v>
+        <v>0.02986</v>
       </c>
     </row>
     <row r="90">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="C90" s="8" t="n">
-        <v>1406304.63</v>
+        <v>1394502.97</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.308475</v>
+        <v>0.305999</v>
       </c>
       <c r="E90" s="9" t="n"/>
     </row>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>2387165.87</v>
+        <v>2393136.89</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.523628</v>
+        <v>0.5251319999999999</v>
       </c>
       <c r="E91" s="9" t="n"/>
     </row>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>604396.12</v>
+        <v>606338.53</v>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.132575</v>
+        <v>0.13305</v>
       </c>
       <c r="E92" s="9" t="n"/>
     </row>
@@ -2242,7 +2242,7 @@
         <v>45523.14</v>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.009986</v>
+        <v>0.009989</v>
       </c>
       <c r="E94" s="9" t="n"/>
     </row>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>10127335.46</v>
+        <v>8690493.68</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>0.066357</v>
+        <v>0.056943</v>
       </c>
     </row>
     <row r="96">
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>73023.05</v>
+        <v>0</v>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.007209999999999999</v>
+        <v>0</v>
       </c>
       <c r="E96" s="9" t="n"/>
     </row>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>72220.78999999999</v>
+        <v>0</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.007130999999999999</v>
+        <v>0</v>
       </c>
       <c r="E97" s="9" t="n"/>
     </row>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>467.75</v>
+        <v>0</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>4.6e-05</v>
+        <v>0</v>
       </c>
       <c r="E99" s="9" t="n"/>
     </row>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="C100" s="8" t="n">
-        <v>334.51</v>
+        <v>0</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>3.3e-05</v>
+        <v>0</v>
       </c>
       <c r="E100" s="9" t="n"/>
     </row>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>6285000.41</v>
+        <v>6224174.28</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.620598</v>
+        <v>0.7162050000000001</v>
       </c>
       <c r="E101" s="9" t="n"/>
     </row>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="C102" s="8" t="n">
-        <v>4936.7</v>
+        <v>0</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.000487</v>
+        <v>0</v>
       </c>
       <c r="E102" s="9" t="n"/>
     </row>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>3129.05</v>
+        <v>0</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.000309</v>
+        <v>0</v>
       </c>
       <c r="E103" s="9" t="n"/>
     </row>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="C104" s="8" t="n">
-        <v>1038.52</v>
+        <v>0</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.000103</v>
+        <v>0</v>
       </c>
       <c r="E104" s="9" t="n"/>
     </row>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>769.12</v>
+        <v>0</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>7.6e-05</v>
+        <v>0</v>
       </c>
       <c r="E105" s="9" t="n"/>
     </row>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="C106" s="8" t="n">
-        <v>1208424.36</v>
+        <v>315098.94</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.119323</v>
+        <v>0.036258</v>
       </c>
       <c r="E106" s="9" t="n"/>
     </row>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>94622.37</v>
+        <v>37433.27</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.009343000000000001</v>
+        <v>0.004307</v>
       </c>
       <c r="E107" s="9" t="n"/>
     </row>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="C108" s="8" t="n">
-        <v>93134.89</v>
+        <v>37433.27</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.009195999999999999</v>
+        <v>0.004307</v>
       </c>
       <c r="E108" s="9" t="n"/>
     </row>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>1487.49</v>
+        <v>0</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.000147</v>
+        <v>0</v>
       </c>
       <c r="E109" s="9" t="n"/>
     </row>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="C110" s="8" t="n">
-        <v>11778.1</v>
+        <v>0</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.001163</v>
+        <v>0</v>
       </c>
       <c r="E110" s="9" t="n"/>
     </row>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>2403.8</v>
+        <v>0</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.000237</v>
+        <v>0</v>
       </c>
       <c r="E111" s="9" t="n"/>
     </row>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="C112" s="8" t="n">
-        <v>685.46</v>
+        <v>0</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>6.8e-05</v>
+        <v>0</v>
       </c>
       <c r="E112" s="9" t="n"/>
     </row>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>4321.03</v>
+        <v>0</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.000427</v>
+        <v>0</v>
       </c>
       <c r="E113" s="9" t="n"/>
     </row>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="C114" s="8" t="n">
-        <v>662.13</v>
+        <v>0</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>6.499999999999999e-05</v>
+        <v>0</v>
       </c>
       <c r="E114" s="9" t="n"/>
     </row>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>2906.92</v>
+        <v>0</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.000287</v>
+        <v>0</v>
       </c>
       <c r="E115" s="9" t="n"/>
     </row>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>798.77</v>
+        <v>0</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>7.900000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="E117" s="9" t="n"/>
     </row>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>2449550.47</v>
+        <v>2113787.19</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.241875</v>
+        <v>0.24323</v>
       </c>
       <c r="E119" s="9" t="n"/>
     </row>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="C120" s="8" t="n">
-        <v>30419.2</v>
+        <v>0</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.003004</v>
+        <v>0</v>
       </c>
       <c r="E120" s="9" t="n"/>
     </row>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>94956.81</v>
+        <v>93868.55</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.009376000000000001</v>
+        <v>0.010801</v>
       </c>
       <c r="E121" s="9" t="n"/>
     </row>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="C122" s="8" t="n">
-        <v>500.6</v>
+        <v>0</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>4.9e-05</v>
+        <v>0</v>
       </c>
       <c r="E122" s="9" t="n"/>
     </row>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>2404.85</v>
+        <v>0</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.000237</v>
+        <v>0</v>
       </c>
       <c r="E123" s="9" t="n"/>
     </row>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>6092.47</v>
+        <v>0</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.000602</v>
+        <v>0</v>
       </c>
       <c r="E125" s="9" t="n"/>
     </row>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="C126" s="8" t="n">
-        <v>233161.28</v>
+        <v>0</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.023023</v>
+        <v>0</v>
       </c>
       <c r="E126" s="9" t="n"/>
     </row>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>85400.49000000001</v>
+        <v>0</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.008433000000000001</v>
+        <v>0</v>
       </c>
       <c r="E127" s="9" t="n"/>
     </row>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="C128" s="8" t="n">
-        <v>1703.7</v>
+        <v>0</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.000168</v>
+        <v>0</v>
       </c>
       <c r="E128" s="9" t="n"/>
     </row>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>1258.64</v>
+        <v>0</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.000124</v>
+        <v>0</v>
       </c>
       <c r="E129" s="9" t="n"/>
     </row>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="C130" s="8" t="n">
-        <v>1982843.11</v>
+        <v>2019918.64</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.195791</v>
+        <v>0.232429</v>
       </c>
       <c r="E130" s="9" t="n"/>
     </row>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>8681.67</v>
+        <v>0</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.000857</v>
+        <v>0</v>
       </c>
       <c r="E131" s="9" t="n"/>
     </row>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="C132" s="8" t="n">
-        <v>1601.39</v>
+        <v>0</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.000158</v>
+        <v>0</v>
       </c>
       <c r="E132" s="9" t="n"/>
     </row>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>526.26</v>
+        <v>0</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>5.2e-05</v>
+        <v>0</v>
       </c>
       <c r="E133" s="9" t="n"/>
     </row>
@@ -3001,13 +3001,13 @@
         </is>
       </c>
       <c r="C134" s="5" t="n">
-        <v>46844.53</v>
+        <v>0</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>0.000307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1511182.22</v>
+        <v>1508929.53</v>
       </c>
       <c r="D135" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>0.009901999999999999</v>
+        <v>0.009887</v>
       </c>
     </row>
     <row r="136">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>1510114.48</v>
+        <v>1508929.53</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.999293</v>
+        <v>1</v>
       </c>
       <c r="E137" s="9" t="n"/>
     </row>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="C138" s="8" t="n">
-        <v>1067.74</v>
+        <v>0</v>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.0007069999999999999</v>
+        <v>0</v>
       </c>
       <c r="E138" s="9" t="n"/>
     </row>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="C140" s="5" t="n">
-        <v>1921346.53</v>
+        <v>1554783.84</v>
       </c>
       <c r="D140" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>0.012589</v>
+        <v>0.010187</v>
       </c>
     </row>
     <row r="141">

--- a/data/informes/cuadro_10_4.xlsx
+++ b/data/informes/cuadro_10_4.xlsx
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>45500596.73</v>
+        <v>45386252.67</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.298134</v>
+        <v>0.297385</v>
       </c>
     </row>
     <row r="5">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>44720946.75</v>
+        <v>44610442.94</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.982865</v>
+        <v>0.982907</v>
       </c>
       <c r="E5" s="9" t="n"/>
     </row>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>13842944.36</v>
+        <v>13779588.2</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.304237</v>
+        <v>0.303607</v>
       </c>
       <c r="E6" s="9" t="n"/>
     </row>
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>12559538.77</v>
+        <v>12547616.58</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.27603</v>
+        <v>0.276463</v>
       </c>
       <c r="E7" s="9" t="n"/>
     </row>
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>10228976.62</v>
+        <v>10170811.89</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.22481</v>
+        <v>0.224095</v>
       </c>
       <c r="E8" s="9" t="n"/>
     </row>
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>8059694.2</v>
+        <v>8082780.53</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.177134</v>
+        <v>0.178089</v>
       </c>
       <c r="E9" s="9" t="n"/>
     </row>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>771308.6</v>
+        <v>767509.53</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.016952</v>
+        <v>0.016911</v>
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>771308.6</v>
+        <v>767509.53</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.016952</v>
+        <v>0.016911</v>
       </c>
       <c r="E12" s="9" t="n"/>
     </row>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>66948393.92</v>
+        <v>67169229.8</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.438667</v>
+        <v>0.440114</v>
       </c>
     </row>
     <row r="14">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>65720967.27</v>
+        <v>65469231.19</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.981666</v>
+        <v>0.974691</v>
       </c>
       <c r="E14" s="9" t="n"/>
     </row>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>678612.26</v>
+        <v>685593.2</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.010136</v>
+        <v>0.010207</v>
       </c>
       <c r="E15" s="9" t="n"/>
     </row>
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>786060.63</v>
+        <v>784748.87</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.011741</v>
+        <v>0.011683</v>
       </c>
       <c r="E16" s="9" t="n"/>
     </row>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1463772.43</v>
+        <v>1463169.02</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.021864</v>
+        <v>0.021783</v>
       </c>
       <c r="E17" s="9" t="n"/>
     </row>
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>275429.17</v>
+        <v>274964.08</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.004114</v>
+        <v>0.004094</v>
       </c>
       <c r="E18" s="9" t="n"/>
     </row>
@@ -811,7 +811,7 @@
         <v>69722.33</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.001041</v>
+        <v>0.001038</v>
       </c>
       <c r="E19" s="9" t="n"/>
     </row>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>46125.94</v>
+        <v>46176.94</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.0006890000000000001</v>
+        <v>0.000687</v>
       </c>
       <c r="E20" s="9" t="n"/>
     </row>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>283534.02</v>
+        <v>283019.87</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.004235</v>
+        <v>0.004214</v>
       </c>
       <c r="E21" s="9" t="n"/>
     </row>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>507708.96</v>
+        <v>507085.23</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.007584</v>
+        <v>0.007549</v>
       </c>
       <c r="E22" s="9" t="n"/>
     </row>
@@ -884,10 +884,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>158573.98</v>
+        <v>158920.11</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.002369</v>
+        <v>0.002366</v>
       </c>
       <c r="E23" s="9" t="n"/>
     </row>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>1903682.25</v>
+        <v>1911281.23</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.028435</v>
+        <v>0.028455</v>
       </c>
       <c r="E24" s="9" t="n"/>
     </row>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>7613288.87</v>
+        <v>7605693.01</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.113719</v>
+        <v>0.113232</v>
       </c>
       <c r="E25" s="9" t="n"/>
     </row>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>5436322.41</v>
+        <v>5428715.95</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.08120200000000001</v>
+        <v>0.080821</v>
       </c>
       <c r="E26" s="9" t="n"/>
     </row>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>2384329.59</v>
+        <v>2393387.2</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.035614</v>
+        <v>0.035632</v>
       </c>
       <c r="E27" s="9" t="n"/>
     </row>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>2101249.84</v>
+        <v>1889982.56</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.031386</v>
+        <v>0.028138</v>
       </c>
       <c r="E28" s="9" t="n"/>
     </row>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>260824.26</v>
+        <v>266174.42</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.003896</v>
+        <v>0.003963</v>
       </c>
       <c r="E29" s="9" t="n"/>
     </row>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>157391.4</v>
+        <v>157346.18</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.002351</v>
+        <v>0.002343</v>
       </c>
       <c r="E30" s="9" t="n"/>
     </row>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>41594338.92</v>
+        <v>41543250.98</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.62129</v>
+        <v>0.618486</v>
       </c>
       <c r="E31" s="9" t="n"/>
     </row>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>1014543.36</v>
+        <v>1487896.53</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.015154</v>
+        <v>0.022151</v>
       </c>
       <c r="E34" s="9" t="n"/>
     </row>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>212883.3</v>
+        <v>212102.08</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.00318</v>
+        <v>0.003158</v>
       </c>
       <c r="E35" s="9" t="n"/>
     </row>
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>22887797.62</v>
+        <v>22841842.13</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.149968</v>
+        <v>0.149667</v>
       </c>
     </row>
     <row r="37">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>16021056.82</v>
+        <v>16013821.55</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.699982</v>
+        <v>0.701074</v>
       </c>
       <c r="E37" s="9" t="n"/>
     </row>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>472236.3</v>
+        <v>473492.32</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.020633</v>
+        <v>0.020729</v>
       </c>
       <c r="E38" s="9" t="n"/>
     </row>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>1072904.43</v>
+        <v>1071905.6</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.046877</v>
+        <v>0.046927</v>
       </c>
       <c r="E39" s="9" t="n"/>
     </row>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>318011.99</v>
+        <v>319372.13</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.013894</v>
+        <v>0.013982</v>
       </c>
       <c r="E40" s="9" t="n"/>
     </row>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>111171.72</v>
+        <v>111654.75</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.004857</v>
+        <v>0.004888</v>
       </c>
       <c r="E41" s="9" t="n"/>
     </row>
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>306435.24</v>
+        <v>308402.51</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.013389</v>
+        <v>0.013502</v>
       </c>
       <c r="E42" s="9" t="n"/>
     </row>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>700207.8100000001</v>
+        <v>699493.05</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.030593</v>
+        <v>0.030623</v>
       </c>
       <c r="E43" s="9" t="n"/>
     </row>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>165779.85</v>
+        <v>166000.3</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.007243</v>
+        <v>0.007267</v>
       </c>
       <c r="E44" s="9" t="n"/>
     </row>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>448641.74</v>
+        <v>449115.11</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.019602</v>
+        <v>0.019662</v>
       </c>
       <c r="E45" s="9" t="n"/>
     </row>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>212081.9</v>
+        <v>212529.33</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.009266</v>
+        <v>0.009304</v>
       </c>
       <c r="E46" s="9" t="n"/>
     </row>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>157256.08</v>
+        <v>158806.73</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.006871</v>
+        <v>0.006952000000000001</v>
       </c>
       <c r="E47" s="9" t="n"/>
     </row>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>325853.52</v>
+        <v>327519.09</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.014237</v>
+        <v>0.014339</v>
       </c>
       <c r="E48" s="9" t="n"/>
     </row>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>591152.49</v>
+        <v>589601.37</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.025828</v>
+        <v>0.025812</v>
       </c>
       <c r="E49" s="9" t="n"/>
     </row>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>384507</v>
+        <v>383676.66</v>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.0168</v>
+        <v>0.016797</v>
       </c>
       <c r="E50" s="9" t="n"/>
     </row>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>1920146.15</v>
+        <v>1916768.16</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.083894</v>
+        <v>0.083915</v>
       </c>
       <c r="E51" s="9" t="n"/>
     </row>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>1187662.32</v>
+        <v>1189586.46</v>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.051891</v>
+        <v>0.05207900000000001</v>
       </c>
       <c r="E52" s="9" t="n"/>
     </row>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>599558.54</v>
+        <v>598507.26</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.026196</v>
+        <v>0.026202</v>
       </c>
       <c r="E53" s="9" t="n"/>
     </row>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>1479894.73</v>
+        <v>1477047.38</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.06465900000000001</v>
+        <v>0.064664</v>
       </c>
       <c r="E54" s="9" t="n"/>
     </row>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>414550.55</v>
+        <v>415080.16</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.018112</v>
+        <v>0.018172</v>
       </c>
       <c r="E55" s="9" t="n"/>
     </row>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>437105.78</v>
+        <v>436349.7</v>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.019098</v>
+        <v>0.019103</v>
       </c>
       <c r="E56" s="9" t="n"/>
     </row>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>280072.79</v>
+        <v>279670.08</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.012237</v>
+        <v>0.012244</v>
       </c>
       <c r="E57" s="9" t="n"/>
     </row>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>1394594.66</v>
+        <v>1390722.62</v>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.06093200000000001</v>
+        <v>0.06088499999999999</v>
       </c>
       <c r="E58" s="9" t="n"/>
     </row>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>435974.94</v>
+        <v>435242.55</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.019048</v>
+        <v>0.019055</v>
       </c>
       <c r="E59" s="9" t="n"/>
     </row>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="C60" s="8" t="n">
-        <v>522289.46</v>
+        <v>522089.39</v>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.02282</v>
+        <v>0.022857</v>
       </c>
       <c r="E60" s="9" t="n"/>
     </row>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>820880.8</v>
+        <v>819053.42</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.035865</v>
+        <v>0.035858</v>
       </c>
       <c r="E61" s="9" t="n"/>
     </row>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>310222.31</v>
+        <v>310383.91</v>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.013554</v>
+        <v>0.013588</v>
       </c>
       <c r="E62" s="9" t="n"/>
     </row>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>96668.66</v>
+        <v>97086.50999999999</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.004224</v>
+        <v>0.00425</v>
       </c>
       <c r="E63" s="9" t="n"/>
     </row>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="C64" s="8" t="n">
-        <v>216989.22</v>
+        <v>217586.16</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.009481</v>
+        <v>0.009526</v>
       </c>
       <c r="E64" s="9" t="n"/>
     </row>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>638205.83</v>
+        <v>637078.84</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.027884</v>
+        <v>0.027891</v>
       </c>
       <c r="E65" s="9" t="n"/>
     </row>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="C66" s="8" t="n">
-        <v>6866740.8</v>
+        <v>6828020.57</v>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.300018</v>
+        <v>0.298926</v>
       </c>
       <c r="E66" s="9" t="n"/>
     </row>
@@ -1760,13 +1760,13 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>969690.79</v>
+        <v>969857.6899999999</v>
       </c>
       <c r="D69" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>0.006353999999999999</v>
+        <v>0.006355</v>
       </c>
     </row>
     <row r="70">
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>709377.4399999999</v>
+        <v>705885</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.73155</v>
+        <v>0.7278230000000001</v>
       </c>
       <c r="E71" s="9" t="n"/>
     </row>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="C72" s="8" t="n">
-        <v>977.92</v>
+        <v>997.33</v>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.001008</v>
+        <v>0.001028</v>
       </c>
       <c r="E72" s="9" t="n"/>
     </row>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>364059.11</v>
+        <v>362261.86</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.375438</v>
+        <v>0.373521</v>
       </c>
       <c r="E75" s="9" t="n"/>
     </row>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="C76" s="8" t="n">
-        <v>332174.59</v>
+        <v>330520.57</v>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.342557</v>
+        <v>0.340793</v>
       </c>
       <c r="E76" s="9" t="n"/>
     </row>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="C78" s="8" t="n">
-        <v>12165.81</v>
+        <v>12105.25</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.012546</v>
+        <v>0.012481</v>
       </c>
       <c r="E78" s="9" t="n"/>
     </row>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>245901.11</v>
+        <v>249631.6</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.253587</v>
+        <v>0.25739</v>
       </c>
       <c r="E79" s="9" t="n"/>
     </row>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>160731.1</v>
+        <v>162771.6</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.165755</v>
+        <v>0.16783</v>
       </c>
       <c r="E81" s="9" t="n"/>
     </row>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>85170.00999999999</v>
+        <v>86859.99000000001</v>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.08783200000000001</v>
+        <v>0.08956</v>
       </c>
       <c r="E82" s="9" t="n"/>
     </row>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>14412.24</v>
+        <v>14341.09</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.014863</v>
+        <v>0.014787</v>
       </c>
       <c r="E83" s="9" t="n"/>
     </row>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="C86" s="8" t="n">
-        <v>14412.24</v>
+        <v>14341.09</v>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.014863</v>
+        <v>0.014787</v>
       </c>
       <c r="E86" s="9" t="n"/>
     </row>
@@ -2142,13 +2142,13 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>4557206.92</v>
+        <v>4598678.16</v>
       </c>
       <c r="D89" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>0.02986</v>
+        <v>0.030132</v>
       </c>
     </row>
     <row r="90">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="C90" s="8" t="n">
-        <v>1394502.97</v>
+        <v>1389815.76</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.305999</v>
+        <v>0.302221</v>
       </c>
       <c r="E90" s="9" t="n"/>
     </row>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>2393136.89</v>
+        <v>2440034.2</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.5251319999999999</v>
+        <v>0.530595</v>
       </c>
       <c r="E91" s="9" t="n"/>
     </row>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>606338.53</v>
+        <v>606193.0600000001</v>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.13305</v>
+        <v>0.131819</v>
       </c>
       <c r="E92" s="9" t="n"/>
     </row>
@@ -2242,7 +2242,7 @@
         <v>45523.14</v>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.009989</v>
+        <v>0.009899</v>
       </c>
       <c r="E94" s="9" t="n"/>
     </row>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>8690493.68</v>
+        <v>8732014.57</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>0.056943</v>
+        <v>0.057215</v>
       </c>
     </row>
     <row r="96">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>6224174.28</v>
+        <v>6277881.41</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.7162050000000001</v>
+        <v>0.71895</v>
       </c>
       <c r="E101" s="9" t="n"/>
     </row>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="C106" s="8" t="n">
-        <v>315098.94</v>
+        <v>313603.15</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.036258</v>
+        <v>0.035914</v>
       </c>
       <c r="E106" s="9" t="n"/>
     </row>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>37433.27</v>
+        <v>37246.91</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.004307</v>
+        <v>0.004266</v>
       </c>
       <c r="E107" s="9" t="n"/>
     </row>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="C108" s="8" t="n">
-        <v>37433.27</v>
+        <v>37246.91</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.004307</v>
+        <v>0.004266</v>
       </c>
       <c r="E108" s="9" t="n"/>
     </row>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>2113787.19</v>
+        <v>2103283.09</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.24323</v>
+        <v>0.24087</v>
       </c>
       <c r="E119" s="9" t="n"/>
     </row>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>93868.55</v>
+        <v>93404.89</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.010801</v>
+        <v>0.010697</v>
       </c>
       <c r="E121" s="9" t="n"/>
     </row>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="C130" s="8" t="n">
-        <v>2019918.64</v>
+        <v>2009878.2</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.232429</v>
+        <v>0.230173</v>
       </c>
       <c r="E130" s="9" t="n"/>
     </row>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="C140" s="5" t="n">
-        <v>1554783.84</v>
+        <v>1411088.49</v>
       </c>
       <c r="D140" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>0.010187</v>
+        <v>0.009245999999999999</v>
       </c>
     </row>
     <row r="141">
